--- a/Protocolo de troca de Mensagens.xlsx
+++ b/Protocolo de troca de Mensagens.xlsx
@@ -20,13 +20,13 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
   <authors>
-    <author>tc={7eb49491-e78a-41ad-ac83-7d9e63b7b32e}</author>
-    <author>tc={bc847c80-e350-45d5-9354-6b5832ac45a1}</author>
-    <author>tc={c7245aa8-0b1f-4a78-b346-71a9b8c7f4ec}</author>
-    <author>tc={e58ef3db-3794-462f-a703-ed844ab37e31}</author>
+    <author>tc={1ff64e3f-e720-4e2f-a9c4-195d59247224}</author>
+    <author>tc={2ff40cc2-2a79-4f5e-bde5-705ed12b0202}</author>
+    <author>tc={9dee28b4-a278-43a3-8946-bb0a612bd080}</author>
+    <author>tc={d25aea21-9a76-4e91-ac7c-6ad92e42e37f}</author>
   </authors>
   <commentList>
-    <comment authorId="0" xr:uid="{7eb49491-e78a-41ad-ac83-7d9e63b7b32e}" ref="F4">
+    <comment authorId="0" xr:uid="{1ff64e3f-e720-4e2f-a9c4-195d59247224}" ref="F4">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -35,7 +35,7 @@
 </t>
       </text>
     </comment>
-    <comment authorId="1" xr:uid="{bc847c80-e350-45d5-9354-6b5832ac45a1}" ref="G4">
+    <comment authorId="1" xr:uid="{2ff40cc2-2a79-4f5e-bde5-705ed12b0202}" ref="G4">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -44,7 +44,7 @@
 </t>
       </text>
     </comment>
-    <comment authorId="2" xr:uid="{c7245aa8-0b1f-4a78-b346-71a9b8c7f4ec}" ref="H4">
+    <comment authorId="2" xr:uid="{9dee28b4-a278-43a3-8946-bb0a612bd080}" ref="H4">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -61,7 +61,7 @@
 </t>
       </text>
     </comment>
-    <comment authorId="3" xr:uid="{e58ef3db-3794-462f-a703-ed844ab37e31}" ref="D4">
+    <comment authorId="3" xr:uid="{d25aea21-9a76-4e91-ac7c-6ad92e42e37f}" ref="D4">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -74,368 +74,343 @@
 </comments>
 </file>
 
-<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
-  <authors>
-    <author>tc={55867c3b-a253-4814-8a75-0e3a0e0e02f6}</author>
-  </authors>
-  <commentList>
-    <comment authorId="0" xr:uid="{55867c3b-a253-4814-8a75-0e3a0e0e02f6}" ref="C34">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Não poder reutilizar o token complica a geração do token
-</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="651" uniqueCount="511">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="510">
+  <si>
+    <t>Requisição</t>
+  </si>
+  <si>
+    <t>CODIGOS DE STATUS DO PROTOCOLO</t>
+  </si>
   <si>
     <t>PROTOCOLO DE TROCA DE MENSAGENS</t>
   </si>
   <si>
-    <t>Requisição</t>
-  </si>
-  <si>
-    <t>CODIGOS DE STATUS DO PROTOCOLO</t>
-  </si>
-  <si>
-    <t>DICIONARIO DE CAMPOS - FORMATO E VALIDACAO</t>
-  </si>
-  <si>
     <t>Resposta</t>
   </si>
   <si>
     <t>Sistemas Distribuidos - BCC / UTFPR-PG - Prof. Dr. Richard Ribeiro | Sistema Inteligente de Reserva de Salas de Reuniao/Estudo em Campus | Responsaveis pelo protocolo: Pedro Silveira e Daniel Jesus | Versao 2.0</t>
   </si>
   <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>Significado</t>
+  </si>
+  <si>
     <t>Campo</t>
   </si>
   <si>
+    <t>Quando o servidor usa</t>
+  </si>
+  <si>
+    <t>Como o cliente deve reagir</t>
+  </si>
+  <si>
+    <t>Onde aparece</t>
+  </si>
+  <si>
+    <t>Formato / regex</t>
+  </si>
+  <si>
+    <t>200</t>
+  </si>
+  <si>
+    <t>Exemplo</t>
+  </si>
+  <si>
+    <t>Regras</t>
+  </si>
+  <si>
+    <t>OK</t>
+  </si>
+  <si>
+    <t>op</t>
+  </si>
+  <si>
+    <t>Operacao executada com sucesso (leitura, atualizacao, remocao, login, logout).</t>
+  </si>
+  <si>
+    <t>Segue o fluxo normal e atualiza a tela com os dados recebidos.</t>
+  </si>
+  <si>
+    <t>201</t>
+  </si>
+  <si>
+    <t>Created</t>
+  </si>
+  <si>
     <t>1. TRANSPORTE E FORMATO DA MENSAGEM</t>
   </si>
   <si>
+    <t>Recurso criado com sucesso: register, create_room, create_reservation.</t>
+  </si>
+  <si>
+    <t>Exibe confirmacao e guarda o id devolvido, quando houver.</t>
+  </si>
+  <si>
+    <t>400</t>
+  </si>
+  <si>
+    <t>Req. e Resp.</t>
+  </si>
+  <si>
     <t>Ação</t>
   </si>
   <si>
-    <t>Onde aparece</t>
-  </si>
-  <si>
-    <t>Formato / regex</t>
-  </si>
-  <si>
-    <t>status</t>
-  </si>
-  <si>
-    <t>Exemplo</t>
+    <t>Bad Request</t>
+  </si>
+  <si>
+    <t>1.1</t>
+  </si>
+  <si>
+    <t>^[a-z_]{3,30}$</t>
+  </si>
+  <si>
+    <t>Campo obrigatorio ausente, valor nulo, tipo invalido, formato reprovado pela regex, JSON invalido, mensagem acima do limite.</t>
+  </si>
+  <si>
+    <t>"login" / "login_response"</t>
+  </si>
+  <si>
+    <t>Mostra o erro de validacao e mantem o formulario preenchido para correcao.</t>
+  </si>
+  <si>
+    <t>Sempre presente. Resposta = op da requisicao + '_response'. Excecao: 'error' em falha de parse.</t>
   </si>
   <si>
     <t>Direção</t>
   </si>
   <si>
+    <t>Arquitetura</t>
+  </si>
+  <si>
     <t>Dados</t>
   </si>
   <si>
-    <t>Regras</t>
-  </si>
-  <si>
-    <t>Significado</t>
-  </si>
-  <si>
-    <t>1.1</t>
+    <t>401</t>
   </si>
   <si>
     <t>JSON</t>
   </si>
   <si>
-    <t>Quando o servidor usa</t>
-  </si>
-  <si>
-    <t>op</t>
-  </si>
-  <si>
-    <t>Como o cliente deve reagir</t>
-  </si>
-  <si>
-    <t>Arquitetura</t>
-  </si>
-  <si>
-    <t>200</t>
-  </si>
-  <si>
-    <t>Req. e Resp.</t>
+    <t>Cliente/servidor com comunicacao por troca de mensagens via sockets. O servidor atende varios clientes simultaneamente (uma thread por conexao).</t>
+  </si>
+  <si>
+    <t>Unauthorized</t>
+  </si>
+  <si>
+    <t>1.2</t>
+  </si>
+  <si>
+    <t>Credenciais incorretas no login; token ausente, invalido, expirado ou ja invalidado por logout.</t>
+  </si>
+  <si>
+    <t>Protocolo de transporte</t>
+  </si>
+  <si>
+    <t>Descarta o token local e envia o usuario de volta para a tela de login.</t>
   </si>
   <si>
     <t>Resposta 200</t>
   </si>
   <si>
-    <t>Cliente/servidor com comunicacao por troca de mensagens via sockets. O servidor atende varios clientes simultaneamente (uma thread por conexao).</t>
-  </si>
-  <si>
-    <t>OK</t>
-  </si>
-  <si>
-    <t>^[a-z_]{3,30}$</t>
-  </si>
-  <si>
-    <t>1.2</t>
+    <t>403</t>
+  </si>
+  <si>
+    <t>^[0-9]{3}$</t>
+  </si>
+  <si>
+    <t>Forbidden</t>
+  </si>
+  <si>
+    <t>"200"</t>
+  </si>
+  <si>
+    <t>TCP. O servidor possui campo para digitacao da porta de escuta; o cliente possui campo para o IP e campo para a porta do servidor a ser contactado.</t>
   </si>
   <si>
     <t>Resposta 401</t>
   </si>
   <si>
-    <t>"login" / "login_response"</t>
-  </si>
-  <si>
-    <t>Operacao executada com sucesso (leitura, atualizacao, remocao, login, logout).</t>
-  </si>
-  <si>
-    <t>Sempre presente. Resposta = op da requisicao + '_response'. Excecao: 'error' em falha de parse.</t>
-  </si>
-  <si>
-    <t>Segue o fluxo normal e atualiza a tela com os dados recebidos.</t>
-  </si>
-  <si>
-    <t>201</t>
-  </si>
-  <si>
-    <t>Created</t>
-  </si>
-  <si>
-    <t>Recurso criado com sucesso: register, create_room, create_reservation.</t>
-  </si>
-  <si>
-    <t>Exibe confirmacao e guarda o id devolvido, quando houver.</t>
+    <t>Token valido, porem sem permissao: usuario comum em operacao de admin, acesso a reserva de terceiro, remocao do ultimo administrador.</t>
+  </si>
+  <si>
+    <t>Codigo numerico como string. Ver aba Codigos de Status.</t>
+  </si>
+  <si>
+    <t>Informa a falta de permissao. Nao repete a requisicao.</t>
+  </si>
+  <si>
+    <t>1.3</t>
+  </si>
+  <si>
+    <t>404</t>
+  </si>
+  <si>
+    <t>message</t>
   </si>
   <si>
     <t>Resposta 400</t>
   </si>
   <si>
-    <t>Protocolo de transporte</t>
+    <t>Codificacao</t>
+  </si>
+  <si>
+    <t>Not Found</t>
   </si>
   <si>
     <t>Resposta 409</t>
   </si>
   <si>
-    <t>400</t>
-  </si>
-  <si>
-    <t>TCP. O servidor possui campo para digitacao da porta de escuta; o cliente possui campo para o IP e campo para a porta do servidor a ser contactado.</t>
-  </si>
-  <si>
-    <t>Bad Request</t>
-  </si>
-  <si>
-    <t>Campo obrigatorio ausente, valor nulo, tipo invalido, formato reprovado pela regex, JSON invalido, mensagem acima do limite.</t>
-  </si>
-  <si>
-    <t>^[0-9]{3}$</t>
-  </si>
-  <si>
-    <t>Mostra o erro de validacao e mantem o formulario preenchido para correcao.</t>
-  </si>
-  <si>
-    <t>"200"</t>
-  </si>
-  <si>
-    <t>1.3</t>
-  </si>
-  <si>
-    <t>Codigo numerico como string. Ver aba Codigos de Status.</t>
-  </si>
-  <si>
-    <t>Codificacao</t>
-  </si>
-  <si>
-    <t>message</t>
-  </si>
-  <si>
-    <t>401</t>
-  </si>
-  <si>
     <t>UTF-8 em todas as mensagens, de ambos os lados.</t>
   </si>
   <si>
+    <t>Recurso inexistente: usuario alvo, sala ou reserva nao encontrados.</t>
+  </si>
+  <si>
     <t>Texto livre, sem acentos</t>
   </si>
   <si>
+    <t>Informa que o registro nao existe e recarrega a listagem.</t>
+  </si>
+  <si>
     <t>1.4</t>
   </si>
   <si>
+    <t>"Login realizado com sucesso"</t>
+  </si>
+  <si>
+    <t>409</t>
+  </si>
+  <si>
     <t>Formato</t>
   </si>
   <si>
-    <t>"Login realizado com sucesso"</t>
+    <t>Usar exatamente o texto definido nas abas de mensagens.</t>
+  </si>
+  <si>
+    <t>Conflict</t>
   </si>
   <si>
     <t>Uma mensagem = um objeto JSON valido, serializado em linha unica (sem quebras de linha internas e sem identacao).</t>
   </si>
   <si>
-    <t>Unauthorized</t>
-  </si>
-  <si>
-    <t>Usar exatamente o texto definido nas abas de mensagens.</t>
+    <t>token</t>
+  </si>
+  <si>
+    <t>Conflito com o estado atual: usuario/email/sala ja cadastrados, sessao ja ativa, horario ja reservado, sala com reservas ativas.</t>
+  </si>
+  <si>
+    <t>Req. e login_response</t>
   </si>
   <si>
     <t>1.5</t>
   </si>
   <si>
-    <t>token</t>
+    <t>Mostra o conflito e oferece alternativa (outro horario, outro nome, logout).</t>
+  </si>
+  <si>
+    <t>^[a-f0-9]{64}$</t>
   </si>
   <si>
     <t>Delimitador (framing)</t>
   </si>
   <si>
-    <t>Credenciais incorretas no login; token ausente, invalido, expirado ou ja invalidado por logout.</t>
-  </si>
-  <si>
-    <t>Req. e login_response</t>
-  </si>
-  <si>
-    <t>^[a-f0-9]{64}$</t>
+    <t>"c0fc3c713f09a433..."</t>
+  </si>
+  <si>
+    <t>500</t>
   </si>
   <si>
     <t>Cada mensagem termina com o caractere LF ('\n'). O receptor le ate o '\n' e trata o conteudo acumulado como uma mensagem completa.</t>
   </si>
   <si>
-    <t>Descarta o token local e envia o usuario de volta para a tela de login.</t>
-  </si>
-  <si>
-    <t>"c0fc3c713f09a433..."</t>
+    <t>Internal Server Error</t>
+  </si>
+  <si>
+    <t>Obrigatorio em toda requisicao, exceto register e login. Gerado no login, invalidado no logout.</t>
+  </si>
+  <si>
+    <t>Falha inesperada no servidor durante o processamento.</t>
+  </si>
+  <si>
+    <t>1.6</t>
+  </si>
+  <si>
+    <t>Informa a falha e permite nova tentativa. Nao descarta o token.</t>
+  </si>
+  <si>
+    <t>Tamanho maximo</t>
+  </si>
+  <si>
+    <t>8192 bytes por mensagem, ja incluindo o '\n'. Mensagem maior e descartada e respondida com status 400.</t>
   </si>
   <si>
     <t>login</t>
   </si>
   <si>
-    <t>1.6</t>
-  </si>
-  <si>
-    <t>Obrigatorio em toda requisicao, exceto register e login. Gerado no login, invalidado no logout.</t>
-  </si>
-  <si>
-    <t>403</t>
-  </si>
-  <si>
-    <t>Tamanho maximo</t>
-  </si>
-  <si>
-    <t>Forbidden</t>
-  </si>
-  <si>
-    <t>8192 bytes por mensagem, ja incluindo o '\n'. Mensagem maior e descartada e respondida com status 400.</t>
-  </si>
-  <si>
-    <t>Token valido, porem sem permissao: usuario comum em operacao de admin, acesso a reserva de terceiro, remocao do ultimo administrador.</t>
+    <t>user</t>
   </si>
   <si>
     <t>1.7</t>
   </si>
   <si>
-    <t>user</t>
-  </si>
-  <si>
     <t>Modelo de interacao</t>
   </si>
   <si>
-    <t>Informa a falta de permissao. Nao repete a requisicao.</t>
-  </si>
-  <si>
     <t>C-&gt;S</t>
   </si>
   <si>
     <t>Requisicao/resposta: toda requisicao do cliente gera exatamente uma resposta do servidor, na mesma conexao.</t>
   </si>
   <si>
-    <t>404</t>
-  </si>
-  <si>
-    <t>Not Found</t>
-  </si>
-  <si>
     <t>1.8</t>
   </si>
   <si>
     <t>Nome da resposta</t>
   </si>
   <si>
-    <t>Recurso inexistente: usuario alvo, sala ou reserva nao encontrados.</t>
-  </si>
-  <si>
     <t>A chave 'op' da resposta e sempre a 'op' da requisicao acrescida do sufixo '_response' (ex.: login -&gt; login_response).</t>
   </si>
   <si>
-    <t>Informa que o registro nao existe e recarrega a listagem.</t>
+    <t xml:space="preserve">        op, user, password</t>
   </si>
   <si>
     <t>1.9</t>
   </si>
   <si>
-    <t>409</t>
-  </si>
-  <si>
     <t>Conexao</t>
   </si>
   <si>
-    <t>Conflict</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        op, user, password</t>
-  </si>
-  <si>
     <t>A conexao e mantida durante a sessao. Timeout de inatividade de 300 s: o servidor encerra a conexao, mas nao invalida o token.</t>
   </si>
   <si>
-    <t>Conflito com o estado atual: usuario/email/sala ja cadastrados, sessao ja ativa, horario ja reservado, sala com reservas ativas.</t>
-  </si>
-  <si>
-    <t>Mostra o conflito e oferece alternativa (outro horario, outro nome, logout).</t>
+    <t>{"op" : "login", "user" : "joao123", "password" : "senha123"}</t>
+  </si>
+  <si>
+    <t>^[a-z]{1,30}$</t>
   </si>
   <si>
     <t>1.10</t>
   </si>
   <si>
-    <t>^[a-z]{1,30}$</t>
-  </si>
-  <si>
     <t>Ordem dos campos</t>
   </si>
   <si>
-    <t>500</t>
+    <t>S-&gt;C</t>
   </si>
   <si>
     <t>Irrelevante. O receptor nunca deve depender da ordem das chaves no JSON.</t>
   </si>
   <si>
-    <t>{"op" : "login", "user" : "joao123", "password" : "senha123"}</t>
-  </si>
-  <si>
-    <t>Internal Server Error</t>
-  </si>
-  <si>
     <t>"joao"</t>
   </si>
   <si>
-    <t>Falha inesperada no servidor durante o processamento.</t>
-  </si>
-  <si>
     <t>2. REGRAS GERAIS DAS CHAVES (base: documento de Requisitos)</t>
   </si>
   <si>
     <t>Sem acentos, sem números, sem espacos, sem caracteres especiais (@ # / $ % c-cedilha), sem emojis, sem nulo. Unico no sistema.</t>
-  </si>
-  <si>
-    <t>Informa a falha e permite nova tentativa. Nao descarta o token.</t>
-  </si>
-  <si>
-    <t>S-&gt;C</t>
-  </si>
-  <si>
-    <t>NOME - SEM NUMERO, SO LETRAS, SEM ESPACO</t>
   </si>
   <si>
     <t>{
@@ -452,13 +427,7 @@
 }</t>
   </si>
   <si>
-    <t>password</t>
-  </si>
-  <si>
-    <t>2.1</t>
-  </si>
-  <si>
-    <t>Chave 'op'</t>
+    <t>NOME - SEM NUMERO, SO LETRAS, SEM ESPACO</t>
   </si>
   <si>
     <t>{
@@ -468,34 +437,31 @@
 }</t>
   </si>
   <si>
+    <t>password</t>
+  </si>
+  <si>
+    <t>Requisicao</t>
+  </si>
+  <si>
+    <t>2.1</t>
+  </si>
+  <si>
+    <t>logout</t>
+  </si>
+  <si>
+    <t>Chave 'op'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        op, token</t>
+  </si>
+  <si>
     <t>Toda mensagem, de requisicao ou de resposta, possui a chave 'op', que define a operacao. E sempre a primeira chave.</t>
   </si>
   <si>
+    <t>{ "op": "logout", "token": "[a-f0-9]{64}" }</t>
+  </si>
+  <si>
     <t>2.2</t>
-  </si>
-  <si>
-    <t>Idioma e estilo</t>
-  </si>
-  <si>
-    <t>logout</t>
-  </si>
-  <si>
-    <t>Todas as chaves em ingles, em snake_case, minusculas, sem acentos.</t>
-  </si>
-  <si>
-    <t>2.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        op, token</t>
-  </si>
-  <si>
-    <t>Tipos</t>
-  </si>
-  <si>
-    <t>{ "op": "logout", "token": "[a-f0-9]{64}" }</t>
-  </si>
-  <si>
-    <t>Todos os valores sao STRINGS. Numeros, booleanos e datas sao representados como STRING (ex.: "capacity": "12", "available": "true").</t>
   </si>
   <si>
     <t>{
@@ -505,10 +471,7 @@
 }</t>
   </si>
   <si>
-    <t>2.4</t>
-  </si>
-  <si>
-    <t>Listas</t>
+    <t>Idioma e estilo</t>
   </si>
   <si>
     <t>{
@@ -518,40 +481,40 @@
 }</t>
   </si>
   <si>
+    <t>Todas as chaves em ingles, em snake_case, minusculas, sem acentos.</t>
+  </si>
+  <si>
+    <t>2.3</t>
+  </si>
+  <si>
+    <t>Tipos</t>
+  </si>
+  <si>
+    <t>register</t>
+  </si>
+  <si>
+    <t>Todos os valores sao STRINGS. Numeros, booleanos e datas sao representados como STRING (ex.: "capacity": "12", "available": "true").</t>
+  </si>
+  <si>
+    <t>2.4</t>
+  </si>
+  <si>
+    <t>op, email, user, password</t>
+  </si>
+  <si>
+    <t>Listas</t>
+  </si>
+  <si>
+    <t>{ "op": "register", "email": "teste@email.com", "user": "joao123", "password": "senha123" }</t>
+  </si>
+  <si>
     <t>Quando a resposta devolve varios registros, usa-se um array JSON de objetos cujos valores tambem sao strings (ex.: "rooms": [ { ... }, { ... } ]).</t>
   </si>
   <si>
+    <t>{ "op": "register_response", "status": "201", "message": "Usuario cadastrado com sucesso" }</t>
+  </si>
+  <si>
     <t>2.5</t>
-  </si>
-  <si>
-    <t>Token</t>
-  </si>
-  <si>
-    <t>Toda requisicao do cliente envia 'token', exceto 'register' e 'login'.</t>
-  </si>
-  <si>
-    <t>register</t>
-  </si>
-  <si>
-    <t>2.6</t>
-  </si>
-  <si>
-    <t>op, email, user, password</t>
-  </si>
-  <si>
-    <t>{ "op": "register", "email": "teste@email.com", "user": "joao123", "password": "senha123" }</t>
-  </si>
-  <si>
-    <t>Toda resposta contem, no minimo: 'op', 'status' e 'message'. Os demais campos dependem da operacao.</t>
-  </si>
-  <si>
-    <t>{ "op": "register_response", "status": "201", "message": "Usuario cadastrado com sucesso" }</t>
-  </si>
-  <si>
-    <t>2.7</t>
-  </si>
-  <si>
-    <t>Status</t>
   </si>
   <si>
     <t>{
@@ -561,73 +524,79 @@
 }</t>
   </si>
   <si>
+    <t>Token</t>
+  </si>
+  <si>
+    <t>{ "op": "register_response", "status": "409", "message": "Usuario ja cadastrado" }</t>
+  </si>
+  <si>
+    <t>^[A-Za-z0-9]{1,20}$</t>
+  </si>
+  <si>
+    <t>Toda requisicao do cliente envia 'token', exceto 'register' e 'login'.</t>
+  </si>
+  <si>
+    <t>"senha123"</t>
+  </si>
+  <si>
+    <t>read_user</t>
+  </si>
+  <si>
+    <t>2.6</t>
+  </si>
+  <si>
+    <t>Somente letras e numeros. Sem espacos, acentos, especiais, emojis ou nulo. Nunca aparece em resposta.</t>
+  </si>
+  <si>
+    <t>C -&gt; S</t>
+  </si>
+  <si>
+    <t>op, token</t>
+  </si>
+  <si>
+    <t>{ "op": "read_user", "token": "[a-f0-9]{64}" }</t>
+  </si>
+  <si>
+    <t>Toda resposta contem, no minimo: 'op', 'status' e 'message'. Os demais campos dependem da operacao.</t>
+  </si>
+  <si>
+    <t>email</t>
+  </si>
+  <si>
+    <t>2.7</t>
+  </si>
+  <si>
+    <t>^[a-z0-9.]+@[a-z0-9]+(\.[a-z]+){1,2}$</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>"joao.silva@email.com"</t>
+  </si>
+  <si>
     <t>'status' e o codigo numerico da resposta, como STRING (ex.: "200").</t>
   </si>
   <si>
-    <t>{ "op": "register_response", "status": "409", "message": "Usuario ja cadastrado" }</t>
+    <t>Unico no sistema. Definido no register e NAO pode ser alterado depois (RNF 5.c).</t>
+  </si>
+  <si>
+    <t>update_user</t>
   </si>
   <si>
     <t>2.8</t>
   </si>
   <si>
+    <t>role</t>
+  </si>
+  <si>
+    <t>op, token, email, user, password</t>
+  </si>
+  <si>
+    <t>Resposta e admin_update_user</t>
+  </si>
+  <si>
     <t>Mensagens de texto</t>
-  </si>
-  <si>
-    <t>Requisicao</t>
-  </si>
-  <si>
-    <t>read_user</t>
-  </si>
-  <si>
-    <t>'message' e escrita em portugues, sem acentos e sem emojis, exatamente como especificado nas abas de mensagens.</t>
-  </si>
-  <si>
-    <t>C -&gt; S</t>
-  </si>
-  <si>
-    <t>^[A-Za-z0-9]{1,20}$</t>
-  </si>
-  <si>
-    <t>op, token</t>
-  </si>
-  <si>
-    <t>"senha123"</t>
-  </si>
-  <si>
-    <t>2.9</t>
-  </si>
-  <si>
-    <t>{ "op": "read_user", "token": "[a-f0-9]{64}" }</t>
-  </si>
-  <si>
-    <t>Campos desconhecidos</t>
-  </si>
-  <si>
-    <t>Somente letras e numeros. Sem espacos, acentos, especiais, emojis ou nulo. Nunca aparece em resposta.</t>
-  </si>
-  <si>
-    <t>Campos nao previstos sao ignorados pelo receptor (garante interoperabilidade entre implementacoes de grupos diferentes).</t>
-  </si>
-  <si>
-    <t>email</t>
-  </si>
-  <si>
-    <t>2.10</t>
-  </si>
-  <si>
-    <t>update_user</t>
-  </si>
-  <si>
-    <t>Campos obrigatorios ausentes</t>
-  </si>
-  <si>
-    <t>Ausencia de campo obrigatorio, campo nulo (null) ou tipo diferente de string resultam em status 400.</t>
-  </si>
-  <si>
-    <t>op, token, email, user, password</t>
-  </si>
-  <si>
-    <t>^[a-z0-9.]+@[a-z0-9]+(\.[a-z]+){1,2}$</t>
   </si>
   <si>
     <t>{ 
@@ -639,22 +608,19 @@
 }</t>
   </si>
   <si>
-    <t>"joao.silva@email.com"</t>
-  </si>
-  <si>
-    <t>2.11</t>
-  </si>
-  <si>
-    <t>Campos vazios</t>
-  </si>
-  <si>
-    <t>Unico no sistema. Definido no register e NAO pode ser alterado depois (RNF 5.c).</t>
+    <t>^(user|admin)$</t>
+  </si>
+  <si>
+    <t>'message' e escrita em portugues, sem acentos e sem emojis, exatamente como especificado nas abas de mensagens.</t>
   </si>
   <si>
     <t>{ "op": "update_user_response", "status": "200", "message": "Dados atualizados com sucesso" }</t>
   </si>
   <si>
-    <t>String vazia ("") em requisicao de atualizacao significa 'nao alterar'. Em requisicao de criacao, e invalida (400).</t>
+    <t>"user"</t>
+  </si>
+  <si>
+    <t>2.9</t>
   </si>
   <si>
     <t>{
@@ -664,37 +630,34 @@
 }</t>
   </si>
   <si>
-    <t>role</t>
-  </si>
-  <si>
-    <t>2.12</t>
+    <t>Todo register nasce "user". Somente admin altera role.</t>
+  </si>
+  <si>
+    <t>Campos desconhecidos</t>
   </si>
   <si>
     <t>{ "op": "update_user_response", "status": "409", "message": "dados ja em uso" }</t>
   </si>
   <si>
-    <t>Sensibilidade a maiusculas</t>
-  </si>
-  <si>
-    <t>Resposta e admin_update_user</t>
-  </si>
-  <si>
-    <t>'op' e os nomes de chaves sao case-sensitive. 'user' e 'email' sao sempre gravados em minusculas.</t>
-  </si>
-  <si>
-    <t>^(user|admin)$</t>
+    <t>Campos nao previstos sao ignorados pelo receptor (garante interoperabilidade entre implementacoes de grupos diferentes).</t>
+  </si>
+  <si>
+    <t>target_user</t>
   </si>
   <si>
     <t>delete_user</t>
   </si>
   <si>
-    <t>"user"</t>
+    <t>Requisicoes admin_*</t>
+  </si>
+  <si>
+    <t>2.10</t>
   </si>
   <si>
     <t>op, token, user, password</t>
   </si>
   <si>
-    <t>Todo register nasce "user". Somente admin altera role.</t>
+    <t>Campos obrigatorios ausentes</t>
   </si>
   <si>
     <t>{ "op": "delete_user", 
@@ -704,118 +667,157 @@
 }</t>
   </si>
   <si>
-    <t>target_user</t>
-  </si>
-  <si>
-    <t>Requisicoes admin_*</t>
+    <t>Ausencia de campo obrigatorio, campo nulo (null) ou tipo diferente de string resultam em status 400.</t>
+  </si>
+  <si>
+    <t>2.11</t>
+  </si>
+  <si>
+    <t>Campos vazios</t>
+  </si>
+  <si>
+    <t>"maria"</t>
+  </si>
+  <si>
+    <t>String vazia ("") em requisicao de atualizacao significa 'nao alterar'. Em requisicao de criacao, e invalida (400).</t>
+  </si>
+  <si>
+    <t>Identifica o usuario alvo da operacao administrativa. Nunca usado para identificar o autor da requisicao.</t>
   </si>
   <si>
     <t>{ "op": "delete_user_response", "status": "200", "message": "Usuario removido com sucesso" }</t>
   </si>
   <si>
+    <t>2.12</t>
+  </si>
+  <si>
+    <t>room_id</t>
+  </si>
+  <si>
+    <t>Sensibilidade a maiusculas</t>
+  </si>
+  <si>
+    <t>{ "op": "delete_user_response", "status": "401", "message": "Token invalido ou expirado" }</t>
+  </si>
+  <si>
+    <t>'op' e os nomes de chaves sao case-sensitive. 'user' e 'email' sao sempre gravados em minusculas.</t>
+  </si>
+  <si>
+    <t>^[0-9]{1,10}$</t>
+  </si>
+  <si>
+    <t>"1"</t>
+  </si>
+  <si>
     <t>3. AUTENTICACAO, TOKEN E PERFIS</t>
   </si>
   <si>
-    <t>{ "op": "delete_user_response", "status": "401", "message": "Token invalido ou expirado" }</t>
-  </si>
-  <si>
-    <t>"maria"</t>
-  </si>
-  <si>
-    <t>Identifica o usuario alvo da operacao administrativa. Nunca usado para identificar o autor da requisicao.</t>
-  </si>
-  <si>
-    <t>room_id</t>
+    <t>Gerado pelo servidor no create_room. Imutavel.</t>
+  </si>
+  <si>
+    <t>{ "op": "delete_user_response", "status": "403", "message": "Permissao insuficiente" }</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>{ "op": "delete_user_response", "status": "404", "message": "Usuario nao encontrado" }</t>
+  </si>
+  <si>
+    <t>Salas</t>
+  </si>
+  <si>
+    <t>^[A-Za-z0-9 -]{1,30}$</t>
+  </si>
+  <si>
+    <t>{ "op": "delete_user_response", "status": "403", "message": "Nao e possivel remover o ultimo administrador" }</t>
+  </si>
+  <si>
+    <t>"Sala de Estudo B12"</t>
+  </si>
+  <si>
+    <t>Nome da sala, unico. Sem acentos.</t>
   </si>
   <si>
     <t>3.1</t>
   </si>
   <si>
-    <t>^[0-9]{1,10}$</t>
-  </si>
-  <si>
-    <t>{ "op": "delete_user_response", "status": "403", "message": "Permissao insuficiente" }</t>
+    <t>capacity</t>
   </si>
   <si>
     <t>Geracao do token</t>
   </si>
   <si>
-    <t>"1"</t>
-  </si>
-  <si>
-    <t>Gerado pelo servidor no create_room. Imutavel.</t>
-  </si>
-  <si>
     <t>Gerado pelo servidor no momento do login: 64 caracteres hexadecimais minusculos, regex ^[a-f0-9]{64}$.</t>
   </si>
   <si>
-    <t>{ "op": "delete_user_response", "status": "404", "message": "Usuario nao encontrado" }</t>
-  </si>
-  <si>
-    <t>name</t>
+    <t>^[1-9][0-9]{0,3}$</t>
+  </si>
+  <si>
+    <t>"12"</t>
   </si>
   <si>
     <t>3.2</t>
   </si>
   <si>
-    <t>Salas</t>
+    <t>Numero de lugares, como string. Limita 'participants' das reservas.</t>
   </si>
   <si>
     <t>Armazenamento</t>
   </si>
   <si>
-    <t>^[A-Za-z0-9 -]{1,30}$</t>
-  </si>
-  <si>
-    <t>{ "op": "delete_user_response", "status": "403", "message": "Nao e possivel remover o ultimo administrador" }</t>
-  </si>
-  <si>
     <t>O servidor armazena o token no banco, associado ao usuario; o cliente guarda o token em memoria durante a sessao.</t>
   </si>
   <si>
-    <t>"Sala de Estudo B12"</t>
-  </si>
-  <si>
-    <t>Nome da sala, unico. Sem acentos.</t>
+    <t>location</t>
   </si>
   <si>
     <t>3.3</t>
   </si>
   <si>
+    <t>^[A-Za-z0-9 ,.-]{1,60}$</t>
+  </si>
+  <si>
     <t>Validade</t>
   </si>
   <si>
-    <t>capacity</t>
+    <t>"Bloco B - 1 andar"</t>
+  </si>
+  <si>
+    <t>Localizacao fisica da sala.</t>
   </si>
   <si>
     <t>30 minutos sem uso. Cada requisicao valida renova a contagem. Token expirado responde 401.</t>
   </si>
   <si>
+    <t>resources</t>
+  </si>
+  <si>
     <t>3.4</t>
   </si>
   <si>
-    <t>^[1-9][0-9]{0,3}$</t>
-  </si>
-  <si>
     <t>Invalidacao</t>
   </si>
   <si>
-    <t>"12"</t>
+    <t>Array de strings</t>
   </si>
   <si>
     <t>O logout invalida o token. Um token invalidado nunca e reutilizado.</t>
   </si>
   <si>
-    <t>Numero de lugares, como string. Limita 'participants' das reservas.</t>
+    <t>["projetor", "tv"]</t>
   </si>
   <si>
     <t>3.5</t>
   </si>
   <si>
+    <t>Lista de recursos. Array vazio quando nao houver.</t>
+  </si>
+  <si>
     <t>Sessao unica</t>
   </si>
   <si>
-    <t>location</t>
+    <t>room_status</t>
   </si>
   <si>
     <t>Um usuario tem no maximo uma sessao ativa. Novo login com sessao ativa responde 409.</t>
@@ -824,63 +826,39 @@
     <t>3.6</t>
   </si>
   <si>
-    <t>^[A-Za-z0-9 ,.-]{1,60}$</t>
-  </si>
-  <si>
     <t>Perfis (role)</t>
   </si>
   <si>
-    <t>"Bloco B - 1 andar"</t>
-  </si>
-  <si>
     <t>"user" (comum) e "admin" (administrador). Todo cadastro por 'register' nasce como "user".</t>
   </si>
   <si>
-    <t>Localizacao fisica da sala.</t>
-  </si>
-  <si>
     <t>3.7</t>
   </si>
   <si>
     <t>Autorizacao</t>
   </si>
   <si>
-    <t>resources</t>
-  </si>
-  <si>
-    <t>Array de strings</t>
-  </si>
-  <si>
     <t>Operacoes com prefixo 'admin_' e o CRUD de salas exigem role "admin". Token valido mas sem permissao responde 403.</t>
   </si>
   <si>
-    <t>["projetor", "tv"]</t>
-  </si>
-  <si>
     <t>3.8</t>
   </si>
   <si>
-    <t>Lista de recursos. Array vazio quando nao houver.</t>
-  </si>
-  <si>
     <t>Identificacao do dono</t>
   </si>
   <si>
-    <t>room_status</t>
-  </si>
-  <si>
     <t>O servidor identifica o autor da requisicao pelo token. O cliente nunca envia o proprio 'user' para dizer quem e.</t>
   </si>
   <si>
     <t>^(active|inactive)$</t>
   </si>
   <si>
+    <t>4. TRATAMENTO DE ERROS DE PROTOCOLO</t>
+  </si>
+  <si>
     <t>"active"</t>
   </si>
   <si>
-    <t>4. TRATAMENTO DE ERROS DE PROTOCOLO</t>
-  </si>
-  <si>
     <t>Sala "inactive" (manutencao) nao aceita novas reservas. Nome distinto de 'status' para nao colidir com o codigo da resposta.</t>
   </si>
   <si>
@@ -890,22 +868,28 @@
     <t>Reservas</t>
   </si>
   <si>
+    <t>4.1</t>
+  </si>
+  <si>
     <t>"27"</t>
   </si>
   <si>
+    <t>JSON invalido</t>
+  </si>
+  <si>
     <t>Gerado pelo servidor no create_reservation. Imutavel.</t>
   </si>
   <si>
-    <t>4.1</t>
+    <t>{"op": "error", "status": "400", "message": "Requisicao invalida"}</t>
   </si>
   <si>
     <t>date</t>
   </si>
   <si>
-    <t>JSON invalido</t>
-  </si>
-  <si>
-    <t>{"op": "error", "status": "400", "message": "Requisicao invalida"}</t>
+    <t>4.2</t>
+  </si>
+  <si>
+    <t>Operacao desconhecida</t>
   </si>
   <si>
     <t>^[0-9]{4}-[0-9]{2}-[0-9]{2}$</t>
@@ -914,27 +898,21 @@
     <t>"2026-09-15"</t>
   </si>
   <si>
-    <t>4.2</t>
-  </si>
-  <si>
-    <t>Operacao desconhecida</t>
+    <t>{"op": "error", "status": "400", "message": "Operacao desconhecida"}</t>
   </si>
   <si>
     <t>Formato ISO AAAA-MM-DD. Nao se reserva data passada (400).</t>
   </si>
   <si>
-    <t>{"op": "error", "status": "400", "message": "Operacao desconhecida"}</t>
-  </si>
-  <si>
     <t>4.3</t>
   </si>
   <si>
+    <t>Mensagem acima do limite</t>
+  </si>
+  <si>
     <t>start_time</t>
   </si>
   <si>
-    <t>Mensagem acima do limite</t>
-  </si>
-  <si>
     <t>{"op": "error", "status": "400", "message": "Mensagem excede o tamanho maximo"}</t>
   </si>
   <si>
@@ -944,12 +922,12 @@
     <t>4.4</t>
   </si>
   <si>
+    <t>Falha interna</t>
+  </si>
+  <si>
     <t>"14:00"</t>
   </si>
   <si>
-    <t>Falha interna</t>
-  </si>
-  <si>
     <t>Qualquer operacao pode responder 500: {"op": "&lt;op&gt;_response", "status": "500", "message": "Erro interno do servidor"}</t>
   </si>
   <si>
@@ -959,60 +937,60 @@
     <t>4.5</t>
   </si>
   <si>
+    <t>Resposta sempre enviada</t>
+  </si>
+  <si>
     <t>end_time</t>
   </si>
   <si>
-    <t>Resposta sempre enviada</t>
-  </si>
-  <si>
     <t>O servidor nunca fecha a conexao sem responder a uma requisicao recebida por completo.</t>
   </si>
   <si>
+    <t>5. CONCORRENCIA (desafio do sistema distribuido)</t>
+  </si>
+  <si>
     <t>"16:00"</t>
   </si>
   <si>
-    <t>5. CONCORRENCIA (desafio do sistema distribuido)</t>
-  </si>
-  <si>
     <t>Deve ser maior que start_time e no mesmo dia (400 caso contrario).</t>
   </si>
   <si>
     <t>topic</t>
   </si>
   <si>
+    <t>5.1</t>
+  </si>
+  <si>
     <t>"Reuniao de projeto"</t>
   </si>
   <si>
-    <t>5.1</t>
+    <t>Regra de ouro</t>
   </si>
   <si>
     <t>Assunto da reserva. Sem acentos.</t>
   </si>
   <si>
-    <t>Regra de ouro</t>
-  </si>
-  <si>
     <t>A verificacao de disponibilidade e a gravacao da reserva ocorrem na MESMA secao critica, protegida por lock por 'room_id'.</t>
   </si>
   <si>
+    <t>5.2</t>
+  </si>
+  <si>
+    <t>Consequencia</t>
+  </si>
+  <si>
     <t>participants</t>
   </si>
   <si>
-    <t>5.2</t>
-  </si>
-  <si>
-    <t>Consequencia</t>
-  </si>
-  <si>
     <t>'check_availability' e informativo: um "true" nao reserva nada e nao garante a reserva seguinte.</t>
   </si>
   <si>
+    <t>5.3</t>
+  </si>
+  <si>
     <t>"6"</t>
   </si>
   <si>
-    <t>5.3</t>
-  </si>
-  <si>
     <t>Reserva duplicada</t>
   </si>
   <si>
@@ -1022,12 +1000,12 @@
     <t>Dois clientes reservando a mesma sala e horario: o primeiro a obter o lock recebe 201, o segundo recebe 409.</t>
   </si>
   <si>
+    <t>5.4</t>
+  </si>
+  <si>
     <t>available</t>
   </si>
   <si>
-    <t>5.4</t>
-  </si>
-  <si>
     <t>Sobreposicao</t>
   </si>
   <si>
@@ -1043,25 +1021,31 @@
     <t>"true"</t>
   </si>
   <si>
+    <t>6. COMO LER AS ABAS DE MENSAGENS</t>
+  </si>
+  <si>
     <t>Booleano como string. Informativo: nao reserva a sala.</t>
   </si>
   <si>
-    <t>6. COMO LER AS ABAS DE MENSAGENS</t>
-  </si>
-  <si>
     <t>count</t>
   </si>
   <si>
     <t>Respostas de listagem</t>
   </si>
   <si>
+    <t>6.1</t>
+  </si>
+  <si>
     <t>"3"</t>
   </si>
   <si>
     <t>Quantidade de itens no array devolvido.</t>
   </si>
   <si>
-    <t>6.1</t>
+    <t>Colunas A a D: acao, direcao, campos enviados e exemplo completo em JSON.</t>
+  </si>
+  <si>
+    <t>6.2</t>
   </si>
   <si>
     <t>created_at</t>
@@ -1070,51 +1054,45 @@
     <t>Respostas de leitura</t>
   </si>
   <si>
-    <t>Colunas A a D: acao, direcao, campos enviados e exemplo completo em JSON.</t>
+    <t>Colunas E a K: direcao e o JSON de cada codigo de status possivel. Celula vazia = aquele codigo nao se aplica aquela operacao.</t>
   </si>
   <si>
     <t>^[0-9]{4}-[0-9]{2}-[0-9]{2} ([01][0-9]|2[0-3]):[0-5][0-9]:[0-5][0-9]$</t>
   </si>
   <si>
-    <t>6.2</t>
+    <t>6.3</t>
+  </si>
+  <si>
+    <t>Observacoes</t>
   </si>
   <si>
     <t>"2026-09-09 14:32:10"</t>
   </si>
   <si>
-    <t>Colunas E a K: direcao e o JSON de cada codigo de status possivel. Celula vazia = aquele codigo nao se aplica aquela operacao.</t>
+    <t>Coluna L: regras especificas da operacao (validacoes, permissoes, efeitos colaterais).</t>
   </si>
   <si>
     <t>Data e hora local do servidor.</t>
   </si>
   <si>
-    <t>6.3</t>
-  </si>
-  <si>
-    <t>Observacoes</t>
+    <t>6.4</t>
+  </si>
+  <si>
+    <t>Exemplos</t>
   </si>
   <si>
     <t>users / rooms / reservations</t>
   </si>
   <si>
-    <t>Coluna L: regras especificas da operacao (validacoes, permissoes, efeitos colaterais).</t>
+    <t>Todos os exemplos usam dados ficticios e tokens validos quanto ao formato. O token dos exemplos e sempre o mesmo apenas por clareza.</t>
   </si>
   <si>
     <t>Array de objetos</t>
   </si>
   <si>
-    <t>6.4</t>
-  </si>
-  <si>
-    <t>Exemplos</t>
-  </si>
-  <si>
     <t>[ { ... }, { ... } ]</t>
   </si>
   <si>
-    <t>Todos os exemplos usam dados ficticios e tokens validos quanto ao formato. O token dos exemplos e sempre o mesmo apenas por clareza.</t>
-  </si>
-  <si>
     <t>Array vazio quando nao houver registros. A resposta continua sendo 200.</t>
   </si>
   <si>
@@ -1127,6 +1105,9 @@
     <t>OBSERVACOES</t>
   </si>
   <si>
+    <t>REQUISICAO</t>
+  </si>
+  <si>
     <t>Acao</t>
   </si>
   <si>
@@ -1151,6 +1132,9 @@
     <t>AUTENTICACAO</t>
   </si>
   <si>
+    <t>OPERACOES DO ADMINISTRADOR (exigem token de role "admin")</t>
+  </si>
+  <si>
     <t>{"op": "register", "email": "joao.silva@email.com", "user": "joao", "password": "senha123"}</t>
   </si>
   <si>
@@ -1169,7 +1153,10 @@
     <t>Unica operacao, junto com login, que nao envia token. Valida user, password e email pelas regex da aba Dicionario de Campos. Todo cadastro nasce com role "user". O cadastro nao cria sessao: o cliente deve fazer login em seguida.</t>
   </si>
   <si>
-    <t>REQUISICAO</t>
+    <t>admin_list_users</t>
+  </si>
+  <si>
+    <t>{"op": "admin_list_users", "token": "c6a07b8585ace1409236251c4eccbe4a2807bb4a7cf1d086de6d603c2794796b"}</t>
   </si>
   <si>
     <t>op, email, password</t>
@@ -1178,6 +1165,9 @@
     <t>{"op": "login", "email": "joao.silva@email.com", "password": "senha123"}</t>
   </si>
   <si>
+    <t>{"op": "admin_list_users_response", "status": "200", "message": "Consulta realizada com sucesso", "count": "2", "users": [{"user": "joao", "email": "joao.silva@email.com", "role": "user"}, {"user": "maria", "email": "maria@email.com", "role": "admin"}]}</t>
+  </si>
+  <si>
     <t>{"op": "login_response", "status": "200", "message": "Login realizado com sucesso", "token": "c0fc3c713f09a43384ac08f7d91fca430dcbc6466fff9284ce4571bdc2c8f9f9", "role": "user"}</t>
   </si>
   <si>
@@ -1187,12 +1177,27 @@
     <t>{"op": "login_response", "status": "401", "message": "Email ou senha incorretos"}</t>
   </si>
   <si>
+    <t>{"op": "admin_list_users_response", "status": "400", "message": "Token em formato invalido"}</t>
+  </si>
+  <si>
+    <t>{"op": "admin_list_users_response", "status": "401", "message": "Token invalido ou expirado"}</t>
+  </si>
+  <si>
+    <t>{"op": "admin_list_users_response", "status": "403", "message": "Permissao insuficiente"}</t>
+  </si>
+  <si>
     <t>{"op": "login_response", "status": "409", "message": "Usuario ja possui sessao ativa"}</t>
   </si>
   <si>
+    <t>Lista todos os cadastros. Nunca devolve senhas. Lista vazia devolve 200 com "count": "0" e "users": [].</t>
+  </si>
+  <si>
     <t>Credenciais corretas: o servidor gera e armazena o token e devolve token e role. Usuario inexistente e senha errada devolvem a MESMA mensagem 401, para nao revelar quais usuarios existem. Sessao ativa: 409 (fazer logout ou aguardar a expiracao de 30 min).</t>
   </si>
   <si>
+    <t>admin_read_user</t>
+  </si>
+  <si>
     <t>{"op": "logout", "token": "c0fc3c713f09a43384ac08f7d91fca430dcbc6466fff9284ce4571bdc2c8f9f9"}</t>
   </si>
   <si>
@@ -1205,42 +1210,117 @@
     <t>{"op": "logout_response", "status": "401", "message": "Token invalido ou expirado"}</t>
   </si>
   <si>
+    <t>op, token, target_user</t>
+  </si>
+  <si>
     <t>O servidor busca o token no banco e o invalida para a proxima sessao. Token ja invalidado responde 401. Apos o 200 o cliente descarta o token e volta a tela de login.</t>
   </si>
   <si>
+    <t>{"op": "admin_read_user", "token": "c6a07b8585ace1409236251c4eccbe4a2807bb4a7cf1d086de6d603c2794796b", "target_user": "joao"}</t>
+  </si>
+  <si>
     <t>CRUD DO PRÓPRIO CADASTRO (usuário comum), o token identifica o autor</t>
   </si>
   <si>
+    <t>{"op": "admin_read_user_response", "status": "200", "message": "Consulta realizada com sucesso", "user": "joao", "email": "joao.silva@email.com", "role": "user", "created_at": "2026-09-09 14:32:10"}</t>
+  </si>
+  <si>
+    <t>{"op": "admin_read_user_response", "status": "400", "message": "Dados em formato invalido"}</t>
+  </si>
+  <si>
+    <t>{"op": "admin_read_user_response", "status": "401", "message": "Token invalido ou expirado"}</t>
+  </si>
+  <si>
+    <t>{"op": "admin_read_user_response", "status": "403", "message": "Permissao insuficiente"}</t>
+  </si>
+  <si>
+    <t>{"op": "admin_read_user_response", "status": "404", "message": "Usuario nao encontrado"}</t>
+  </si>
+  <si>
+    <t>Le o cadastro de qualquer usuario. 'target_user' e sempre o alvo; o autor continua sendo identificado pelo token.</t>
+  </si>
+  <si>
+    <t>admin_update_user</t>
+  </si>
+  <si>
+    <t>op, token, target_user, user, password, role</t>
+  </si>
+  <si>
+    <t>{"op": "admin_update_user", "token": "c6a07b8585ace1409236251c4eccbe4a2807bb4a7cf1d086de6d603c2794796b", "target_user": "joao", "user": "joao", "password": "", "role": "admin"}</t>
+  </si>
+  <si>
     <t>{"op": "read_user", "token": "c0fc3c713f09a43384ac08f7d91fca430dcbc6466fff9284ce4571bdc2c8f9f9"}</t>
   </si>
   <si>
+    <t>{"op": "admin_update_user_response", "status": "200", "message": "Dados atualizados com sucesso"}</t>
+  </si>
+  <si>
+    <t>{"op": "admin_update_user_response", "status": "400", "message": "Dados em formato invalido"}</t>
+  </si>
+  <si>
+    <t>{"op": "admin_update_user_response", "status": "401", "message": "Token invalido ou expirado"}</t>
+  </si>
+  <si>
     <t>{"op": "read_user_response", "status": "200", "message": "Consulta realizada com sucesso", "user": "joao", "email": "joao.silva@email.com", "role": "user", "created_at": "2026-09-09 14:32:10"}</t>
   </si>
   <si>
+    <t>{"op": "admin_update_user_response", "status": "403", "message": "Permissao insuficiente"}</t>
+  </si>
+  <si>
+    <t>{"op": "admin_update_user_response", "status": "404", "message": "Usuario nao encontrado"}</t>
+  </si>
+  <si>
     <t>{"op": "read_user_response", "status": "400", "message": "Token em formato invalido"}</t>
   </si>
   <si>
+    <t>{"op": "admin_update_user_response", "status": "409", "message": "Usuario ja esta em uso"}</t>
+  </si>
+  <si>
     <t>{"op": "read_user_response", "status": "401", "message": "Token invalido ou expirado"}</t>
   </si>
   <si>
+    <t>Mesmas regras de update_user, e o admin ainda pode alterar 'role'. O email tambem nao pode ser alterado. Rebaixar o proprio role quando se e o unico admin responde 403 (Nao e possivel remover o ultimo administrador).</t>
+  </si>
+  <si>
+    <t>admin_delete_user</t>
+  </si>
+  <si>
     <t>Le apenas o proprio cadastro; nao ha campo de usuario alvo. A senha nunca e devolvida. Para ler o cadastro de outro usuario existe admin_read_user.</t>
   </si>
   <si>
+    <t>{"op": "admin_delete_user", "token": "c6a07b8585ace1409236251c4eccbe4a2807bb4a7cf1d086de6d603c2794796b", "target_user": "joao"}</t>
+  </si>
+  <si>
+    <t>{"op": "admin_delete_user_response", "status": "200", "message": "Usuario removido com sucesso"}</t>
+  </si>
+  <si>
     <t>{"op": "update_user", "token": "c0fc3c713f09a43384ac08f7d91fca430dcbc6466fff9284ce4571bdc2c8f9f9", "user": "joao", "password": "novasenha1"}</t>
   </si>
   <si>
+    <t>{"op": "admin_delete_user_response", "status": "400", "message": "Dados em formato invalido"}</t>
+  </si>
+  <si>
+    <t>{"op": "admin_delete_user_response", "status": "401", "message": "Token invalido ou expirado"}</t>
+  </si>
+  <si>
     <t>{"op": "update_user_response", "status": "200", "message": "Dados atualizados com sucesso"}</t>
   </si>
   <si>
+    <t>{"op": "admin_delete_user_response", "status": "403", "message": "Permissao insuficiente"}</t>
+  </si>
+  <si>
     <t>{"op": "update_user_response", "status": "400", "message": "Dados em formato invalido"}</t>
   </si>
   <si>
-    <t>OPERACOES DO ADMINISTRADOR (exigem token de role "admin")</t>
+    <t>{"op": "admin_delete_user_response", "status": "404", "message": "Usuario nao encontrado"}</t>
   </si>
   <si>
     <t>{"op": "update_user_response", "status": "401", "message": "Token invalido ou expirado"}</t>
   </si>
   <si>
+    <t>Remover o ultimo administrador responde 403 com a mensagem "Nao e possivel remover o ultimo administrador". A sessao do usuario removido e encerrada e suas reservas futuras sao canceladas.</t>
+  </si>
+  <si>
     <t>{"op": "update_user_response", "status": "409", "message": "Usuario ja esta em uso"}</t>
   </si>
   <si>
@@ -1265,109 +1345,7 @@
     <t>{"op": "delete_user_response", "status": "403", "message": "Nao e possivel remover o ultimo administrador"}</t>
   </si>
   <si>
-    <t>admin_list_users</t>
-  </si>
-  <si>
     <t>Remove o proprio cadastro; o alvo vem do token e a senha confirma a operacao. Senha incorreta responde 401. O token e invalidado junto e as reservas futuras do usuario sao canceladas. Remocao de outro usuario e feita por admin_delete_user.</t>
-  </si>
-  <si>
-    <t>{"op": "admin_list_users", "token": "c6a07b8585ace1409236251c4eccbe4a2807bb4a7cf1d086de6d603c2794796b"}</t>
-  </si>
-  <si>
-    <t>{"op": "admin_list_users_response", "status": "200", "message": "Consulta realizada com sucesso", "count": "2", "users": [{"user": "joao", "email": "joao.silva@email.com", "role": "user"}, {"user": "maria", "email": "maria@email.com", "role": "admin"}]}</t>
-  </si>
-  <si>
-    <t>{"op": "admin_list_users_response", "status": "400", "message": "Token em formato invalido"}</t>
-  </si>
-  <si>
-    <t>{"op": "admin_list_users_response", "status": "401", "message": "Token invalido ou expirado"}</t>
-  </si>
-  <si>
-    <t>{"op": "admin_list_users_response", "status": "403", "message": "Permissao insuficiente"}</t>
-  </si>
-  <si>
-    <t>Lista todos os cadastros. Nunca devolve senhas. Lista vazia devolve 200 com "count": "0" e "users": [].</t>
-  </si>
-  <si>
-    <t>admin_read_user</t>
-  </si>
-  <si>
-    <t>op, token, target_user</t>
-  </si>
-  <si>
-    <t>{"op": "admin_read_user", "token": "c6a07b8585ace1409236251c4eccbe4a2807bb4a7cf1d086de6d603c2794796b", "target_user": "joao"}</t>
-  </si>
-  <si>
-    <t>{"op": "admin_read_user_response", "status": "200", "message": "Consulta realizada com sucesso", "user": "joao", "email": "joao.silva@email.com", "role": "user", "created_at": "2026-09-09 14:32:10"}</t>
-  </si>
-  <si>
-    <t>{"op": "admin_read_user_response", "status": "400", "message": "Dados em formato invalido"}</t>
-  </si>
-  <si>
-    <t>{"op": "admin_read_user_response", "status": "401", "message": "Token invalido ou expirado"}</t>
-  </si>
-  <si>
-    <t>{"op": "admin_read_user_response", "status": "403", "message": "Permissao insuficiente"}</t>
-  </si>
-  <si>
-    <t>{"op": "admin_read_user_response", "status": "404", "message": "Usuario nao encontrado"}</t>
-  </si>
-  <si>
-    <t>Le o cadastro de qualquer usuario. 'target_user' e sempre o alvo; o autor continua sendo identificado pelo token.</t>
-  </si>
-  <si>
-    <t>admin_update_user</t>
-  </si>
-  <si>
-    <t>op, token, target_user, user, password, role</t>
-  </si>
-  <si>
-    <t>{"op": "admin_update_user", "token": "c6a07b8585ace1409236251c4eccbe4a2807bb4a7cf1d086de6d603c2794796b", "target_user": "joao", "user": "joao", "password": "", "role": "admin"}</t>
-  </si>
-  <si>
-    <t>{"op": "admin_update_user_response", "status": "200", "message": "Dados atualizados com sucesso"}</t>
-  </si>
-  <si>
-    <t>{"op": "admin_update_user_response", "status": "400", "message": "Dados em formato invalido"}</t>
-  </si>
-  <si>
-    <t>{"op": "admin_update_user_response", "status": "401", "message": "Token invalido ou expirado"}</t>
-  </si>
-  <si>
-    <t>{"op": "admin_update_user_response", "status": "403", "message": "Permissao insuficiente"}</t>
-  </si>
-  <si>
-    <t>{"op": "admin_update_user_response", "status": "404", "message": "Usuario nao encontrado"}</t>
-  </si>
-  <si>
-    <t>{"op": "admin_update_user_response", "status": "409", "message": "Usuario ja esta em uso"}</t>
-  </si>
-  <si>
-    <t>Mesmas regras de update_user, e o admin ainda pode alterar 'role'. O email tambem nao pode ser alterado. Rebaixar o proprio role quando se e o unico admin responde 403 (Nao e possivel remover o ultimo administrador).</t>
-  </si>
-  <si>
-    <t>admin_delete_user</t>
-  </si>
-  <si>
-    <t>{"op": "admin_delete_user", "token": "c6a07b8585ace1409236251c4eccbe4a2807bb4a7cf1d086de6d603c2794796b", "target_user": "joao"}</t>
-  </si>
-  <si>
-    <t>{"op": "admin_delete_user_response", "status": "200", "message": "Usuario removido com sucesso"}</t>
-  </si>
-  <si>
-    <t>{"op": "admin_delete_user_response", "status": "400", "message": "Dados em formato invalido"}</t>
-  </si>
-  <si>
-    <t>{"op": "admin_delete_user_response", "status": "401", "message": "Token invalido ou expirado"}</t>
-  </si>
-  <si>
-    <t>{"op": "admin_delete_user_response", "status": "403", "message": "Permissao insuficiente"}</t>
-  </si>
-  <si>
-    <t>{"op": "admin_delete_user_response", "status": "404", "message": "Usuario nao encontrado"}</t>
-  </si>
-  <si>
-    <t>Remover o ultimo administrador responde 403 com a mensagem "Nao e possivel remover o ultimo administrador". A sessao do usuario removido e encerrada e suas reservas futuras sao canceladas.</t>
   </si>
   <si>
     <t>CRUD DE SALAS - criar, alterar e remover exigem role "admin"; ler e listar sao liberados a qualquer usuario logado</t>
@@ -1680,9 +1658,10 @@
     </font>
     <font>
       <b/>
-      <sz val="16.0"/>
+      <sz val="14.0"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -1692,17 +1671,11 @@
     </font>
     <font>
       <b/>
-      <sz val="14.0"/>
+      <sz val="16.0"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
     </font>
     <font/>
-    <font>
-      <sz val="10.0"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-    </font>
     <font>
       <b/>
       <sz val="10.0"/>
@@ -1711,16 +1684,21 @@
     </font>
     <font>
       <b/>
+      <sz val="10.0"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10.0"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
       <sz val="14.0"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10.0"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
     </font>
     <font>
       <b/>
@@ -1770,14 +1748,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF45818E"/>
+        <bgColor rgb="FF45818E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF1F3864"/>
         <bgColor rgb="FF1F3864"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF45818E"/>
-        <bgColor rgb="FF45818E"/>
+        <fgColor rgb="FF2F5597"/>
+        <bgColor rgb="FF2F5597"/>
       </patternFill>
     </fill>
     <fill>
@@ -1788,8 +1772,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF2F5597"/>
-        <bgColor rgb="FF2F5597"/>
+        <fgColor rgb="FFE2EFDA"/>
+        <bgColor rgb="FFE2EFDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -1800,20 +1784,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6D9EEB"/>
-        <bgColor rgb="FF6D9EEB"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE2EFDA"/>
-        <bgColor rgb="FFE2EFDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FF6D9EEB"/>
+        <bgColor rgb="FF6D9EEB"/>
       </patternFill>
     </fill>
     <fill>
@@ -1965,73 +1943,73 @@
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="2" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="3" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="6" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="4" fillId="6" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="5" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="4" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="6" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="7" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="8" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="6" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="7" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="8" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="7" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="8" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="9" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="4" fillId="8" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="7" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="9" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="8" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="9" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="7" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="9" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="4" fillId="9" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="4" fillId="9" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center"/>
@@ -2039,7 +2017,7 @@
     <xf borderId="0" fillId="10" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="11" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="11" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="10" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
@@ -2051,11 +2029,11 @@
     <xf borderId="0" fillId="10" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="0" fillId="10" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="4" fillId="11" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="10" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="10" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
@@ -2067,11 +2045,11 @@
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="10" fontId="12" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
+    <xf borderId="4" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
     <xf borderId="0" fillId="10" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="10" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" vertical="center"/>
@@ -2094,7 +2072,7 @@
     <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="5" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="6" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
@@ -2108,36 +2086,36 @@
     <xf borderId="9" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="10" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="11" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="12" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="5" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="5" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="12" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="12" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="4" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="13" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="12" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="13" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="14" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="9" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="8" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="4" fillId="8" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="9" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="6" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="14" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="8" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="11" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
@@ -2151,10 +2129,6 @@
 </file>
 
 <file path=xl/documenttasks/documenttask1.xml><?xml version="1.0" encoding="utf-8"?>
-<Tasks xmlns="http://schemas.microsoft.com/office/tasks/2019/documenttasks"/>
-</file>
-
-<file path=xl/documenttasks/documenttask2.xml><?xml version="1.0" encoding="utf-8"?>
 <Tasks xmlns="http://schemas.microsoft.com/office/tasks/2019/documenttasks"/>
 </file>
 
@@ -2192,8 +2166,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <x18tc:person displayName="GABRIEL JOSE MONTEIRO" id="{3f9615ef-d1d5-4cda-8101-aa1fb57c859b}" providerId="google-sheets"/>
-  <x18tc:person displayName="ATOS AIRES ARRUDA" id="{ac4dcffe-6d11-4bec-86ed-45b831a33687}" providerId="google-sheets"/>
+  <x18tc:person displayName="ATOS AIRES ARRUDA" id="{c443cc45-8dd5-4900-ac1c-24f7a384e57a}" providerId="google-sheets"/>
 </x18tc:personList>
 </file>
 
@@ -2393,35 +2366,27 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:ThreadedComments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <x18tc:threadedComment ref="D4" dT="2026-08-26T18:12:07.00" personId="{ac4dcffe-6d11-4bec-86ed-45b831a33687}" id="{e58ef3db-3794-462f-a703-ed844ab37e31}" done="1">
+  <x18tc:threadedComment ref="D4" dT="2026-08-26T18:12:07.00" personId="{c443cc45-8dd5-4900-ac1c-24f7a384e57a}" id="{d25aea21-9a76-4e91-ac7c-6ad92e42e37f}" done="1">
     <x18tc:text xml:space="preserve">Não falta senha??</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="G4" dT="2026-08-26T18:24:23.00" personId="{ac4dcffe-6d11-4bec-86ed-45b831a33687}" id="{bc847c80-e350-45d5-9354-6b5832ac45a1}" done="1">
+  <x18tc:threadedComment ref="G4" dT="2026-08-26T18:24:23.00" personId="{c443cc45-8dd5-4900-ac1c-24f7a384e57a}" id="{2ff40cc2-2a79-4f5e-bde5-705ed12b0202}" done="1">
     <x18tc:text xml:space="preserve">como respondemos que não deu certo ???</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="F4" dT="2026-08-26T18:25:03.00" personId="{ac4dcffe-6d11-4bec-86ed-45b831a33687}" id="{7eb49491-e78a-41ad-ac83-7d9e63b7b32e}" done="1">
+  <x18tc:threadedComment ref="F4" dT="2026-08-26T18:25:03.00" personId="{c443cc45-8dd5-4900-ac1c-24f7a384e57a}" id="{1ff64e3f-e720-4e2f-a9c4-195d59247224}" done="1">
     <x18tc:text xml:space="preserve">pq precisa de op na resposta ??</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="H4" dT="2026-08-27T17:58:49.00" personId="{ac4dcffe-6d11-4bec-86ed-45b831a33687}" id="{c7245aa8-0b1f-4a78-b346-71a9b8c7f4ec}" done="1">
+  <x18tc:threadedComment ref="H4" dT="2026-08-27T17:58:49.00" personId="{c443cc45-8dd5-4900-ac1c-24f7a384e57a}" id="{9dee28b4-a278-43a3-8946-bb0a612bd080}" done="1">
     <x18tc:text xml:space="preserve">remover
 3 total reactions
 ATOS AIRES ARRUDA reacted with 🆗 at 27/08/2026, 17:59 UTC
 ATOS AIRES ARRUDA reacted with ❎ at 27/08/2026, 17:59 UTC
 LEANDRO MARTINS MACHADO HYEDA reacted with 🆗 at 27/08/2026, 17:59 UTC</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="H4" dT="2026-08-27T17:59:18.00" personId="{ac4dcffe-6d11-4bec-86ed-45b831a33687}" id="{8527b408-5342-4f18-83dd-bc40c393e7c7}" parentId="{c7245aa8-0b1f-4a78-b346-71a9b8c7f4ec}">
+  <x18tc:threadedComment ref="H4" dT="2026-08-27T17:59:18.00" personId="{c443cc45-8dd5-4900-ac1c-24f7a384e57a}" id="{628f78b7-bfbb-4bbb-ba38-56442695db37}" parentId="{9dee28b4-a278-43a3-8946-bb0a612bd080}">
     <x18tc:text xml:space="preserve">Marked as resolved</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="H4" dT="2026-08-27T17:59:25.00" personId="{ac4dcffe-6d11-4bec-86ed-45b831a33687}" id="{ab2ea70e-c655-4505-b8bd-6db81b6526bd}" parentId="{c7245aa8-0b1f-4a78-b346-71a9b8c7f4ec}">
+  <x18tc:threadedComment ref="H4" dT="2026-08-27T17:59:25.00" personId="{c443cc45-8dd5-4900-ac1c-24f7a384e57a}" id="{e63a4a41-632b-4057-bd2f-499724c501cf}" parentId="{9dee28b4-a278-43a3-8946-bb0a612bd080}">
     <x18tc:text xml:space="preserve">Reopened</x18tc:text>
-  </x18tc:threadedComment>
-</x18tc:ThreadedComments>
-</file>
-
-<file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:ThreadedComments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <x18tc:threadedComment ref="C34" dT="2026-09-23T17:57:30.00" personId="{3f9615ef-d1d5-4cda-8101-aa1fb57c859b}" id="{55867c3b-a253-4814-8a75-0e3a0e0e02f6}" done="0">
-    <x18tc:text xml:space="preserve">Não poder reutilizar o token complica a geração do token</x18tc:text>
   </x18tc:threadedComment>
 </x18tc:ThreadedComments>
 </file>
@@ -2446,55 +2411,55 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="J1" s="8"/>
-      <c r="K1" s="8"/>
-      <c r="L1" s="8"/>
-      <c r="M1" s="8"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="J1" s="11"/>
+      <c r="K1" s="11"/>
+      <c r="L1" s="11"/>
+      <c r="M1" s="11"/>
     </row>
     <row r="2">
-      <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
-      <c r="L2" s="8"/>
-      <c r="M2" s="8"/>
+      <c r="J2" s="11"/>
+      <c r="K2" s="11"/>
+      <c r="L2" s="11"/>
+      <c r="M2" s="11"/>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="G3" s="21" t="s">
-        <v>30</v>
-      </c>
-      <c r="H3" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="I3" s="21" t="s">
-        <v>41</v>
-      </c>
-      <c r="J3" s="23"/>
-      <c r="K3" s="23"/>
-      <c r="L3" s="23"/>
-      <c r="M3" s="23"/>
+      <c r="A3" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="E3" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="G3" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="H3" s="23" t="s">
+        <v>58</v>
+      </c>
+      <c r="I3" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="J3" s="24"/>
+      <c r="K3" s="24"/>
+      <c r="L3" s="24"/>
+      <c r="M3" s="24"/>
       <c r="N3" s="25"/>
       <c r="O3" s="25"/>
       <c r="P3" s="25"/>
@@ -2512,149 +2477,149 @@
     </row>
     <row r="4">
       <c r="A4" s="26" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="B4" s="28" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="C4" s="30" t="s">
-        <v>96</v>
-      </c>
-      <c r="D4" s="32" t="s">
-        <v>105</v>
+        <v>99</v>
+      </c>
+      <c r="D4" s="31" t="s">
+        <v>103</v>
       </c>
       <c r="E4" s="33" t="s">
+        <v>107</v>
+      </c>
+      <c r="F4" s="31" t="s">
         <v>112</v>
       </c>
-      <c r="F4" s="32" t="s">
-        <v>114</v>
-      </c>
-      <c r="G4" s="32" t="s">
+      <c r="G4" s="31" t="s">
+        <v>113</v>
+      </c>
+      <c r="H4" s="31"/>
+      <c r="I4" s="35" t="s">
         <v>115</v>
-      </c>
-      <c r="H4" s="32"/>
-      <c r="I4" s="35" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="5" ht="117.0" customHeight="1">
       <c r="A5" s="26" t="s">
+        <v>119</v>
+      </c>
+      <c r="B5" s="28" t="s">
+        <v>94</v>
+      </c>
+      <c r="C5" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="D5" s="31" t="s">
         <v>123</v>
       </c>
-      <c r="B5" s="28" t="s">
-        <v>83</v>
-      </c>
-      <c r="C5" s="30" t="s">
-        <v>126</v>
-      </c>
-      <c r="D5" s="32" t="s">
-        <v>128</v>
-      </c>
       <c r="E5" s="33" t="s">
-        <v>112</v>
-      </c>
-      <c r="F5" s="32" t="s">
-        <v>130</v>
-      </c>
-      <c r="G5" s="32" t="s">
-        <v>133</v>
-      </c>
-      <c r="H5" s="32"/>
+        <v>107</v>
+      </c>
+      <c r="F5" s="31" t="s">
+        <v>125</v>
+      </c>
+      <c r="G5" s="31" t="s">
+        <v>127</v>
+      </c>
+      <c r="H5" s="31"/>
       <c r="I5" s="36"/>
     </row>
     <row r="6">
       <c r="A6" s="26" t="s">
+        <v>131</v>
+      </c>
+      <c r="B6" s="28" t="s">
+        <v>94</v>
+      </c>
+      <c r="C6" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="D6" s="31" t="s">
+        <v>136</v>
+      </c>
+      <c r="E6" s="33" t="s">
+        <v>107</v>
+      </c>
+      <c r="F6" s="31" t="s">
         <v>138</v>
       </c>
-      <c r="B6" s="28" t="s">
-        <v>83</v>
-      </c>
-      <c r="C6" s="30" t="s">
+      <c r="G6" s="31"/>
+      <c r="H6" s="31" t="s">
         <v>140</v>
       </c>
-      <c r="D6" s="32" t="s">
-        <v>141</v>
-      </c>
-      <c r="E6" s="33" t="s">
-        <v>112</v>
-      </c>
-      <c r="F6" s="32" t="s">
-        <v>143</v>
-      </c>
-      <c r="G6" s="32"/>
-      <c r="H6" s="32" t="s">
-        <v>146</v>
-      </c>
-      <c r="I6" s="32" t="s">
-        <v>148</v>
+      <c r="I6" s="31" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="7" ht="74.25" customHeight="1">
       <c r="A7" s="26" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="B7" s="28" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="C7" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="D7" s="32" t="s">
-        <v>159</v>
+        <v>150</v>
+      </c>
+      <c r="D7" s="31" t="s">
+        <v>151</v>
       </c>
       <c r="E7" s="33" t="s">
-        <v>112</v>
-      </c>
-      <c r="F7" s="32"/>
-      <c r="G7" s="32"/>
-      <c r="H7" s="32"/>
-      <c r="I7" s="32"/>
+        <v>107</v>
+      </c>
+      <c r="F7" s="31"/>
+      <c r="G7" s="31"/>
+      <c r="H7" s="31"/>
+      <c r="I7" s="31"/>
     </row>
     <row r="8">
       <c r="A8" s="26" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="B8" s="28" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="C8" s="30" t="s">
-        <v>168</v>
-      </c>
-      <c r="D8" s="32" t="s">
-        <v>170</v>
+        <v>163</v>
+      </c>
+      <c r="D8" s="31" t="s">
+        <v>166</v>
       </c>
       <c r="E8" s="33" t="s">
-        <v>112</v>
-      </c>
-      <c r="F8" s="32" t="s">
+        <v>107</v>
+      </c>
+      <c r="F8" s="31" t="s">
+        <v>169</v>
+      </c>
+      <c r="G8" s="31"/>
+      <c r="H8" s="35" t="s">
+        <v>172</v>
+      </c>
+      <c r="I8" s="31" t="s">
         <v>175</v>
-      </c>
-      <c r="G8" s="32"/>
-      <c r="H8" s="35" t="s">
-        <v>177</v>
-      </c>
-      <c r="I8" s="32" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="9" ht="154.5" customHeight="1">
       <c r="A9" s="26" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="B9" s="28" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="C9" s="28" t="s">
-        <v>187</v>
-      </c>
-      <c r="D9" s="32" t="s">
-        <v>189</v>
-      </c>
-      <c r="E9" s="37" t="s">
-        <v>112</v>
-      </c>
-      <c r="F9" s="32" t="s">
-        <v>192</v>
+        <v>181</v>
+      </c>
+      <c r="D9" s="31" t="s">
+        <v>183</v>
+      </c>
+      <c r="E9" s="38" t="s">
+        <v>107</v>
+      </c>
+      <c r="F9" s="31" t="s">
+        <v>190</v>
       </c>
       <c r="G9" s="39" t="s">
         <v>194</v>
@@ -2665,10 +2630,10 @@
         <v>200</v>
       </c>
       <c r="K9" s="41" t="s">
+        <v>202</v>
+      </c>
+      <c r="L9" s="41" t="s">
         <v>205</v>
-      </c>
-      <c r="L9" s="41" t="s">
-        <v>211</v>
       </c>
       <c r="M9" s="42"/>
       <c r="N9" s="42"/>
@@ -10639,536 +10604,536 @@
   </cols>
   <sheetData>
     <row r="1" ht="30.0" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
+      <c r="A1" s="3" t="s">
+        <v>2</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="5"/>
     </row>
     <row r="2" ht="30.0" customHeight="1">
-      <c r="A2" s="7" t="s">
-        <v>5</v>
+      <c r="A2" s="9" t="s">
+        <v>4</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="5"/>
     </row>
     <row r="4" ht="21.75" customHeight="1">
-      <c r="A4" s="10" t="s">
-        <v>7</v>
+      <c r="A4" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="5"/>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="17" t="s">
-        <v>26</v>
+      <c r="A5" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="B6" s="22" t="s">
-        <v>40</v>
-      </c>
-      <c r="C6" s="24" t="s">
+      <c r="A6" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" s="19" t="s">
         <v>43</v>
       </c>
+      <c r="C6" s="20" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="B7" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="C7" s="17" t="s">
-        <v>54</v>
+      <c r="A7" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="B8" s="22" t="s">
-        <v>57</v>
-      </c>
-      <c r="C8" s="24" t="s">
-        <v>59</v>
+      <c r="A8" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="B9" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="C9" s="17" t="s">
-        <v>68</v>
+      <c r="A9" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="20" t="s">
-        <v>72</v>
-      </c>
-      <c r="B10" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="C10" s="24" t="s">
-        <v>77</v>
+      <c r="A10" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="C10" s="20" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="B11" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="C11" s="17" t="s">
-        <v>84</v>
+      <c r="A11" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="20" t="s">
-        <v>87</v>
-      </c>
-      <c r="B12" s="22" t="s">
-        <v>88</v>
-      </c>
-      <c r="C12" s="24" t="s">
-        <v>90</v>
+      <c r="A12" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="C12" s="20" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="B13" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="C13" s="17" t="s">
-        <v>97</v>
+      <c r="A13" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="C13" s="15" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="20" t="s">
-        <v>100</v>
-      </c>
-      <c r="B14" s="22" t="s">
-        <v>102</v>
-      </c>
-      <c r="C14" s="24" t="s">
-        <v>104</v>
+      <c r="A14" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="C14" s="20" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="16" ht="21.75" customHeight="1">
-      <c r="A16" s="10" t="s">
-        <v>109</v>
+      <c r="A16" s="13" t="s">
+        <v>110</v>
       </c>
       <c r="B16" s="4"/>
       <c r="C16" s="5"/>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="B17" s="14" t="s">
+      <c r="A17" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="C17" s="17" t="s">
+      <c r="B17" s="12" t="s">
         <v>120</v>
       </c>
+      <c r="C17" s="15" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="20" t="s">
-        <v>121</v>
-      </c>
-      <c r="B18" s="22" t="s">
-        <v>122</v>
-      </c>
-      <c r="C18" s="24" t="s">
+      <c r="A18" s="17" t="s">
         <v>124</v>
       </c>
+      <c r="B18" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="C18" s="20" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="s">
-        <v>125</v>
-      </c>
-      <c r="B19" s="14" t="s">
-        <v>127</v>
-      </c>
-      <c r="C19" s="17" t="s">
+      <c r="A19" s="14" t="s">
         <v>129</v>
       </c>
+      <c r="B19" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="C19" s="15" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="20" t="s">
-        <v>131</v>
-      </c>
-      <c r="B20" s="22" t="s">
-        <v>132</v>
-      </c>
-      <c r="C20" s="24" t="s">
-        <v>134</v>
+      <c r="A20" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="B20" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="C20" s="20" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="s">
-        <v>135</v>
-      </c>
-      <c r="B21" s="14" t="s">
-        <v>136</v>
-      </c>
-      <c r="C21" s="17" t="s">
-        <v>137</v>
+      <c r="A21" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="20" t="s">
-        <v>139</v>
-      </c>
-      <c r="B22" s="22" t="s">
-        <v>4</v>
-      </c>
-      <c r="C22" s="24" t="s">
-        <v>142</v>
+      <c r="A22" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="B22" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="C22" s="20" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="s">
-        <v>144</v>
-      </c>
-      <c r="B23" s="14" t="s">
-        <v>145</v>
-      </c>
-      <c r="C23" s="17" t="s">
-        <v>147</v>
+      <c r="A23" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="C23" s="15" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="20" t="s">
-        <v>149</v>
-      </c>
-      <c r="B24" s="22" t="s">
-        <v>150</v>
-      </c>
-      <c r="C24" s="24" t="s">
-        <v>153</v>
+      <c r="A24" s="17" t="s">
+        <v>161</v>
+      </c>
+      <c r="B24" s="19" t="s">
+        <v>165</v>
+      </c>
+      <c r="C24" s="20" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="B25" s="14" t="s">
-        <v>160</v>
-      </c>
-      <c r="C25" s="17" t="s">
-        <v>162</v>
+      <c r="A25" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="C25" s="15" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="20" t="s">
-        <v>164</v>
-      </c>
-      <c r="B26" s="22" t="s">
-        <v>166</v>
-      </c>
-      <c r="C26" s="24" t="s">
-        <v>167</v>
+      <c r="A26" s="17" t="s">
+        <v>180</v>
+      </c>
+      <c r="B26" s="19" t="s">
+        <v>182</v>
+      </c>
+      <c r="C26" s="20" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="12" t="s">
-        <v>172</v>
-      </c>
-      <c r="B27" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="C27" s="17" t="s">
-        <v>176</v>
+      <c r="A27" s="14" t="s">
+        <v>185</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="C27" s="15" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="20" t="s">
-        <v>179</v>
-      </c>
-      <c r="B28" s="22" t="s">
-        <v>181</v>
-      </c>
-      <c r="C28" s="24" t="s">
-        <v>183</v>
+      <c r="A28" s="17" t="s">
+        <v>191</v>
+      </c>
+      <c r="B28" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="C28" s="20" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="29"/>
     <row r="30" ht="21.75" customHeight="1">
-      <c r="A30" s="10" t="s">
-        <v>193</v>
+      <c r="A30" s="13" t="s">
+        <v>198</v>
       </c>
       <c r="B30" s="4"/>
       <c r="C30" s="5"/>
     </row>
     <row r="31">
-      <c r="A31" s="12" t="s">
-        <v>198</v>
-      </c>
-      <c r="B31" s="14" t="s">
-        <v>201</v>
-      </c>
-      <c r="C31" s="17" t="s">
-        <v>204</v>
+      <c r="A31" s="14" t="s">
+        <v>208</v>
+      </c>
+      <c r="B31" s="12" t="s">
+        <v>210</v>
+      </c>
+      <c r="C31" s="15" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="20" t="s">
-        <v>207</v>
-      </c>
-      <c r="B32" s="22" t="s">
-        <v>209</v>
-      </c>
-      <c r="C32" s="24" t="s">
-        <v>212</v>
+      <c r="A32" s="17" t="s">
+        <v>214</v>
+      </c>
+      <c r="B32" s="19" t="s">
+        <v>216</v>
+      </c>
+      <c r="C32" s="20" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="12" t="s">
-        <v>215</v>
-      </c>
-      <c r="B33" s="14" t="s">
-        <v>216</v>
-      </c>
-      <c r="C33" s="17" t="s">
-        <v>218</v>
+      <c r="A33" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="B33" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="C33" s="15" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="20" t="s">
-        <v>219</v>
-      </c>
-      <c r="B34" s="22" t="s">
-        <v>221</v>
-      </c>
-      <c r="C34" s="24" t="s">
-        <v>223</v>
+      <c r="A34" s="17" t="s">
+        <v>226</v>
+      </c>
+      <c r="B34" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="C34" s="20" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="B35" s="14" t="s">
-        <v>226</v>
-      </c>
-      <c r="C35" s="17" t="s">
-        <v>228</v>
+      <c r="A35" s="14" t="s">
+        <v>231</v>
+      </c>
+      <c r="B35" s="12" t="s">
+        <v>233</v>
+      </c>
+      <c r="C35" s="15" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="20" t="s">
-        <v>229</v>
-      </c>
-      <c r="B36" s="22" t="s">
-        <v>231</v>
-      </c>
-      <c r="C36" s="24" t="s">
-        <v>233</v>
+      <c r="A36" s="17" t="s">
+        <v>236</v>
+      </c>
+      <c r="B36" s="19" t="s">
+        <v>237</v>
+      </c>
+      <c r="C36" s="20" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="12" t="s">
-        <v>235</v>
-      </c>
-      <c r="B37" s="14" t="s">
-        <v>236</v>
-      </c>
-      <c r="C37" s="17" t="s">
+      <c r="A37" s="14" t="s">
         <v>239</v>
       </c>
+      <c r="B37" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="C37" s="15" t="s">
+        <v>241</v>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="20" t="s">
-        <v>241</v>
-      </c>
-      <c r="B38" s="22" t="s">
+      <c r="A38" s="17" t="s">
+        <v>242</v>
+      </c>
+      <c r="B38" s="19" t="s">
         <v>243</v>
       </c>
-      <c r="C38" s="24" t="s">
-        <v>245</v>
+      <c r="C38" s="20" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="39"/>
     <row r="40" ht="21.75" customHeight="1">
-      <c r="A40" s="10" t="s">
-        <v>248</v>
+      <c r="A40" s="13" t="s">
+        <v>246</v>
       </c>
       <c r="B40" s="4"/>
       <c r="C40" s="5"/>
     </row>
     <row r="41">
-      <c r="A41" s="12" t="s">
-        <v>254</v>
-      </c>
-      <c r="B41" s="14" t="s">
-        <v>256</v>
-      </c>
-      <c r="C41" s="17" t="s">
+      <c r="A41" s="14" t="s">
+        <v>251</v>
+      </c>
+      <c r="B41" s="12" t="s">
+        <v>253</v>
+      </c>
+      <c r="C41" s="15" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="17" t="s">
         <v>257</v>
       </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="20" t="s">
-        <v>260</v>
-      </c>
-      <c r="B42" s="22" t="s">
+      <c r="B42" s="19" t="s">
+        <v>258</v>
+      </c>
+      <c r="C42" s="20" t="s">
         <v>261</v>
       </c>
-      <c r="C42" s="24" t="s">
+    </row>
+    <row r="43">
+      <c r="A43" s="14" t="s">
         <v>263</v>
       </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="12" t="s">
+      <c r="B43" s="12" t="s">
         <v>264</v>
       </c>
-      <c r="B43" s="14" t="s">
+      <c r="C43" s="15" t="s">
         <v>266</v>
       </c>
-      <c r="C43" s="17" t="s">
-        <v>267</v>
-      </c>
     </row>
     <row r="44">
-      <c r="A44" s="20" t="s">
+      <c r="A44" s="17" t="s">
+        <v>268</v>
+      </c>
+      <c r="B44" s="19" t="s">
         <v>269</v>
       </c>
-      <c r="B44" s="22" t="s">
+      <c r="C44" s="20" t="s">
         <v>271</v>
       </c>
-      <c r="C44" s="24" t="s">
-        <v>272</v>
-      </c>
     </row>
     <row r="45">
-      <c r="A45" s="12" t="s">
+      <c r="A45" s="14" t="s">
+        <v>273</v>
+      </c>
+      <c r="B45" s="12" t="s">
         <v>274</v>
       </c>
-      <c r="B45" s="14" t="s">
+      <c r="C45" s="15" t="s">
         <v>276</v>
-      </c>
-      <c r="C45" s="17" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="46"/>
     <row r="47" ht="21.75" customHeight="1">
-      <c r="A47" s="10" t="s">
-        <v>279</v>
+      <c r="A47" s="13" t="s">
+        <v>277</v>
       </c>
       <c r="B47" s="4"/>
       <c r="C47" s="5"/>
     </row>
     <row r="48">
-      <c r="A48" s="12" t="s">
+      <c r="A48" s="14" t="s">
+        <v>281</v>
+      </c>
+      <c r="B48" s="12" t="s">
         <v>283</v>
       </c>
-      <c r="B48" s="14" t="s">
+      <c r="C48" s="15" t="s">
         <v>285</v>
       </c>
-      <c r="C48" s="17" t="s">
+    </row>
+    <row r="49">
+      <c r="A49" s="17" t="s">
         <v>286</v>
       </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="20" t="s">
-        <v>288</v>
-      </c>
-      <c r="B49" s="22" t="s">
+      <c r="B49" s="19" t="s">
+        <v>287</v>
+      </c>
+      <c r="C49" s="20" t="s">
         <v>289</v>
       </c>
-      <c r="C49" s="24" t="s">
+    </row>
+    <row r="50">
+      <c r="A50" s="14" t="s">
         <v>290</v>
       </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="12" t="s">
+      <c r="B50" s="12" t="s">
         <v>292</v>
       </c>
-      <c r="B50" s="14" t="s">
-        <v>293</v>
-      </c>
-      <c r="C50" s="17" t="s">
+      <c r="C50" s="15" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="17" t="s">
         <v>295</v>
       </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="20" t="s">
+      <c r="B51" s="19" t="s">
         <v>297</v>
       </c>
-      <c r="B51" s="22" t="s">
-        <v>298</v>
-      </c>
-      <c r="C51" s="24" t="s">
-        <v>300</v>
+      <c r="C51" s="20" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="52"/>
     <row r="53" ht="21.75" customHeight="1">
-      <c r="A53" s="10" t="s">
-        <v>304</v>
+      <c r="A53" s="13" t="s">
+        <v>302</v>
       </c>
       <c r="B53" s="4"/>
       <c r="C53" s="5"/>
     </row>
     <row r="54">
-      <c r="A54" s="12" t="s">
+      <c r="A54" s="14" t="s">
+        <v>306</v>
+      </c>
+      <c r="B54" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="C54" s="15" t="s">
         <v>309</v>
       </c>
-      <c r="B54" s="14" t="s">
-        <v>151</v>
-      </c>
-      <c r="C54" s="17" t="s">
-        <v>312</v>
-      </c>
     </row>
     <row r="55">
-      <c r="A55" s="20" t="s">
-        <v>314</v>
-      </c>
-      <c r="B55" s="22" t="s">
-        <v>4</v>
-      </c>
-      <c r="C55" s="24" t="s">
+      <c r="A55" s="17" t="s">
+        <v>310</v>
+      </c>
+      <c r="B55" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="C55" s="20" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="14" t="s">
+        <v>315</v>
+      </c>
+      <c r="B56" s="12" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="12" t="s">
+      <c r="C56" s="15" t="s">
         <v>318</v>
       </c>
-      <c r="B56" s="14" t="s">
-        <v>319</v>
-      </c>
-      <c r="C56" s="17" t="s">
+    </row>
+    <row r="57">
+      <c r="A57" s="17" t="s">
+        <v>320</v>
+      </c>
+      <c r="B57" s="19" t="s">
         <v>321</v>
       </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="20" t="s">
+      <c r="C57" s="20" t="s">
         <v>323</v>
-      </c>
-      <c r="B57" s="22" t="s">
-        <v>324</v>
-      </c>
-      <c r="C57" s="24" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="58"/>
@@ -12128,8 +12093,7 @@
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.25" right="0.25" top="0.75"/>
   <pageSetup paperSize="5" orientation="landscape"/>
-  <drawing r:id="rId4"/>
-  <legacyDrawing r:id="rId5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -12150,136 +12114,136 @@
   <sheetData>
     <row r="1" ht="24.0" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
       <c r="D1" s="5"/>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" s="9" t="s">
+      <c r="A2" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="D2" s="9" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="16" t="s">
+      <c r="B4" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="19" t="s">
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C5" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="D3" s="19" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="B4" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="C4" s="19" t="s">
+    </row>
+    <row r="6">
+      <c r="A6" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="D4" s="19" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="12" t="s">
+      <c r="B6" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="D6" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="C5" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="D5" s="17" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="B6" s="24" t="s">
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="B8" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="C6" s="24" t="s">
+      <c r="C8" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="D8" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="D6" s="24" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="12" t="s">
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="C9" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="B7" s="17" t="s">
-        <v>76</v>
-      </c>
-      <c r="C7" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="D7" s="17" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="20" t="s">
+      <c r="D9" s="15" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="B10" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="C10" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="B8" s="24" t="s">
-        <v>86</v>
-      </c>
-      <c r="C8" s="24" t="s">
-        <v>89</v>
-      </c>
-      <c r="D8" s="24" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="B9" s="17" t="s">
-        <v>95</v>
-      </c>
-      <c r="C9" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="D9" s="17" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="20" t="s">
-        <v>103</v>
-      </c>
-      <c r="B10" s="24" t="s">
-        <v>106</v>
-      </c>
-      <c r="C10" s="24" t="s">
-        <v>108</v>
-      </c>
-      <c r="D10" s="24" t="s">
-        <v>111</v>
+      <c r="D10" s="20" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="21"/>
@@ -13290,457 +13254,455 @@
   </cols>
   <sheetData>
     <row r="1" ht="24.0" customHeight="1">
-      <c r="A1" s="2" t="s">
-        <v>3</v>
-      </c>
+      <c r="A1" s="2"/>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
       <c r="D1" s="4"/>
       <c r="E1" s="5"/>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="9" t="s">
+      <c r="A2" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>15</v>
+      <c r="C2" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="C3" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="D3" s="17" t="s">
+      <c r="A3" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="E3" s="15" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="D4" s="24" t="s">
-        <v>48</v>
-      </c>
-      <c r="E4" s="24" t="s">
-        <v>50</v>
+      <c r="A4" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="E4" s="20" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="B5" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="D5" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="E5" s="17" t="s">
-        <v>61</v>
+      <c r="A5" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="22" t="s">
-        <v>63</v>
-      </c>
-      <c r="B6" s="24" t="s">
-        <v>66</v>
-      </c>
-      <c r="C6" s="24" t="s">
-        <v>67</v>
-      </c>
-      <c r="D6" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="E6" s="24" t="s">
+      <c r="A6" s="19" t="s">
         <v>73</v>
+      </c>
+      <c r="B6" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="D6" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="E6" s="20" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="27" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="B7" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" s="31" t="s">
-        <v>101</v>
-      </c>
-      <c r="D7" s="31" t="s">
-        <v>107</v>
-      </c>
-      <c r="E7" s="31" t="s">
-        <v>110</v>
+        <v>25</v>
+      </c>
+      <c r="C7" s="32" t="s">
+        <v>104</v>
+      </c>
+      <c r="D7" s="32" t="s">
+        <v>109</v>
+      </c>
+      <c r="E7" s="32" t="s">
+        <v>111</v>
       </c>
       <c r="F7" s="34" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="22" t="s">
+      <c r="A8" s="19" t="s">
         <v>116</v>
       </c>
-      <c r="B8" s="24" t="s">
-        <v>151</v>
-      </c>
-      <c r="C8" s="24" t="s">
+      <c r="B8" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="E8" s="20" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="15" t="s">
         <v>155</v>
       </c>
-      <c r="D8" s="24" t="s">
+      <c r="D9" s="15" t="s">
         <v>157</v>
       </c>
-      <c r="E8" s="24" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="14" t="s">
-        <v>163</v>
-      </c>
-      <c r="B9" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="17" t="s">
-        <v>169</v>
-      </c>
-      <c r="D9" s="17" t="s">
-        <v>171</v>
-      </c>
-      <c r="E9" s="17" t="s">
-        <v>174</v>
+      <c r="E9" s="15" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="22" t="s">
-        <v>178</v>
-      </c>
-      <c r="B10" s="24" t="s">
-        <v>182</v>
-      </c>
-      <c r="C10" s="24" t="s">
-        <v>184</v>
-      </c>
-      <c r="D10" s="24" t="s">
-        <v>186</v>
-      </c>
-      <c r="E10" s="24" t="s">
-        <v>188</v>
+      <c r="A10" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="B10" s="20" t="s">
+        <v>164</v>
+      </c>
+      <c r="C10" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="D10" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="E10" s="20" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="14" t="s">
-        <v>190</v>
-      </c>
-      <c r="B11" s="17" t="s">
-        <v>191</v>
-      </c>
-      <c r="C11" s="38" t="s">
-        <v>101</v>
-      </c>
-      <c r="D11" s="38" t="s">
-        <v>195</v>
-      </c>
-      <c r="E11" s="17" t="s">
+      <c r="A11" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>179</v>
+      </c>
+      <c r="C11" s="37" t="s">
+        <v>104</v>
+      </c>
+      <c r="D11" s="37" t="s">
+        <v>187</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="19" t="s">
+        <v>192</v>
+      </c>
+      <c r="B12" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="20" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="22" t="s">
+      <c r="D12" s="20" t="s">
         <v>197</v>
       </c>
-      <c r="B12" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="C12" s="24" t="s">
+      <c r="E12" s="20" t="s">
         <v>199</v>
       </c>
-      <c r="D12" s="24" t="s">
-        <v>202</v>
-      </c>
-      <c r="E12" s="24" t="s">
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="B13" s="15" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="14" t="s">
+      <c r="C13" s="15" t="s">
+        <v>204</v>
+      </c>
+      <c r="D13" s="15" t="s">
         <v>206</v>
       </c>
-      <c r="B13" s="17" t="s">
-        <v>208</v>
-      </c>
-      <c r="C13" s="17" t="s">
-        <v>210</v>
-      </c>
-      <c r="D13" s="17" t="s">
+      <c r="E13" s="15" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="19" t="s">
+        <v>209</v>
+      </c>
+      <c r="B14" s="20" t="s">
+        <v>203</v>
+      </c>
+      <c r="C14" s="20" t="s">
+        <v>212</v>
+      </c>
+      <c r="D14" s="20" t="s">
         <v>213</v>
       </c>
-      <c r="E13" s="17" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="22" t="s">
-        <v>217</v>
-      </c>
-      <c r="B14" s="24" t="s">
-        <v>208</v>
-      </c>
-      <c r="C14" s="24" t="s">
+      <c r="E14" s="20" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>203</v>
+      </c>
+      <c r="C15" s="15" t="s">
         <v>220</v>
       </c>
-      <c r="D14" s="24" t="s">
+      <c r="D15" s="15" t="s">
         <v>222</v>
       </c>
-      <c r="E14" s="24" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="14" t="s">
-        <v>227</v>
-      </c>
-      <c r="B15" s="17" t="s">
-        <v>208</v>
-      </c>
-      <c r="C15" s="17" t="s">
+      <c r="E15" s="15" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="19" t="s">
+        <v>225</v>
+      </c>
+      <c r="B16" s="20" t="s">
+        <v>203</v>
+      </c>
+      <c r="C16" s="20" t="s">
+        <v>228</v>
+      </c>
+      <c r="D16" s="20" t="s">
         <v>230</v>
       </c>
-      <c r="D15" s="17" t="s">
+      <c r="E16" s="20" t="s">
         <v>232</v>
       </c>
-      <c r="E15" s="17" t="s">
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="s">
         <v>234</v>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="22" t="s">
-        <v>237</v>
-      </c>
-      <c r="B16" s="24" t="s">
-        <v>208</v>
-      </c>
-      <c r="C16" s="24" t="s">
-        <v>238</v>
-      </c>
-      <c r="D16" s="24" t="s">
-        <v>240</v>
-      </c>
-      <c r="E16" s="24" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="14" t="s">
-        <v>244</v>
-      </c>
-      <c r="B17" s="17" t="s">
-        <v>208</v>
-      </c>
-      <c r="C17" s="17" t="s">
-        <v>246</v>
-      </c>
-      <c r="D17" s="17" t="s">
+      <c r="B17" s="15" t="s">
+        <v>203</v>
+      </c>
+      <c r="C17" s="15" t="s">
+        <v>245</v>
+      </c>
+      <c r="D17" s="15" t="s">
         <v>247</v>
       </c>
-      <c r="E17" s="17" t="s">
+      <c r="E17" s="15" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="19" t="s">
         <v>249</v>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="22" t="s">
+      <c r="B18" s="20" t="s">
         <v>250</v>
       </c>
-      <c r="B18" s="24" t="s">
-        <v>251</v>
-      </c>
-      <c r="C18" s="24" t="s">
-        <v>199</v>
-      </c>
-      <c r="D18" s="24" t="s">
+      <c r="C18" s="20" t="s">
+        <v>196</v>
+      </c>
+      <c r="D18" s="20" t="s">
         <v>252</v>
       </c>
-      <c r="E18" s="24" t="s">
-        <v>253</v>
+      <c r="E18" s="20" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="14" t="s">
-        <v>255</v>
-      </c>
-      <c r="B19" s="17" t="s">
-        <v>251</v>
-      </c>
-      <c r="C19" s="17" t="s">
-        <v>258</v>
-      </c>
-      <c r="D19" s="17" t="s">
+      <c r="A19" s="12" t="s">
+        <v>256</v>
+      </c>
+      <c r="B19" s="15" t="s">
+        <v>250</v>
+      </c>
+      <c r="C19" s="15" t="s">
         <v>259</v>
       </c>
-      <c r="E19" s="17" t="s">
+      <c r="D19" s="15" t="s">
+        <v>260</v>
+      </c>
+      <c r="E19" s="15" t="s">
         <v>262</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="22" t="s">
+      <c r="A20" s="19" t="s">
         <v>265</v>
       </c>
-      <c r="B20" s="24" t="s">
-        <v>251</v>
-      </c>
-      <c r="C20" s="24" t="s">
-        <v>268</v>
-      </c>
-      <c r="D20" s="24" t="s">
+      <c r="B20" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="C20" s="20" t="s">
+        <v>267</v>
+      </c>
+      <c r="D20" s="20" t="s">
         <v>270</v>
       </c>
-      <c r="E20" s="24" t="s">
-        <v>273</v>
+      <c r="E20" s="20" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="14" t="s">
+      <c r="A21" s="12" t="s">
         <v>275</v>
       </c>
-      <c r="B21" s="17" t="s">
-        <v>251</v>
-      </c>
-      <c r="C21" s="17" t="s">
-        <v>268</v>
-      </c>
-      <c r="D21" s="17" t="s">
+      <c r="B21" s="15" t="s">
+        <v>250</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>267</v>
+      </c>
+      <c r="D21" s="15" t="s">
         <v>278</v>
       </c>
-      <c r="E21" s="17" t="s">
+      <c r="E21" s="15" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="19" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="B22" s="24" t="s">
-        <v>251</v>
-      </c>
-      <c r="C22" s="24" t="s">
-        <v>230</v>
-      </c>
-      <c r="D22" s="24" t="s">
+      <c r="B22" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="C22" s="20" t="s">
+        <v>220</v>
+      </c>
+      <c r="D22" s="20" t="s">
         <v>282</v>
       </c>
-      <c r="E22" s="24" t="s">
+      <c r="E22" s="20" t="s">
         <v>284</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="14" t="s">
-        <v>287</v>
-      </c>
-      <c r="B23" s="17" t="s">
-        <v>251</v>
-      </c>
-      <c r="C23" s="17" t="s">
-        <v>220</v>
-      </c>
-      <c r="D23" s="17" t="s">
+      <c r="A23" s="12" t="s">
+        <v>288</v>
+      </c>
+      <c r="B23" s="15" t="s">
+        <v>250</v>
+      </c>
+      <c r="C23" s="15" t="s">
+        <v>212</v>
+      </c>
+      <c r="D23" s="15" t="s">
         <v>291</v>
       </c>
-      <c r="E23" s="17" t="s">
-        <v>294</v>
+      <c r="E23" s="15" t="s">
+        <v>293</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="22" t="s">
+      <c r="A24" s="19" t="s">
         <v>296</v>
       </c>
-      <c r="B24" s="24" t="s">
-        <v>299</v>
-      </c>
-      <c r="C24" s="24" t="s">
+      <c r="B24" s="20" t="s">
+        <v>298</v>
+      </c>
+      <c r="C24" s="20" t="s">
+        <v>300</v>
+      </c>
+      <c r="D24" s="20" t="s">
         <v>301</v>
       </c>
-      <c r="D24" s="24" t="s">
-        <v>302</v>
-      </c>
-      <c r="E24" s="24" t="s">
+      <c r="E24" s="20" t="s">
         <v>303</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="14" t="s">
+      <c r="A25" s="12" t="s">
+        <v>304</v>
+      </c>
+      <c r="B25" s="15" t="s">
         <v>305</v>
       </c>
-      <c r="B25" s="17" t="s">
-        <v>306</v>
-      </c>
-      <c r="C25" s="17" t="s">
-        <v>199</v>
-      </c>
-      <c r="D25" s="17" t="s">
+      <c r="C25" s="15" t="s">
+        <v>196</v>
+      </c>
+      <c r="D25" s="15" t="s">
         <v>307</v>
       </c>
-      <c r="E25" s="17" t="s">
+      <c r="E25" s="15" t="s">
         <v>308</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="22" t="s">
-        <v>310</v>
-      </c>
-      <c r="B26" s="24" t="s">
+      <c r="A26" s="19" t="s">
         <v>311</v>
       </c>
-      <c r="C26" s="24" t="s">
-        <v>313</v>
-      </c>
-      <c r="D26" s="24" t="s">
-        <v>315</v>
-      </c>
-      <c r="E26" s="24" t="s">
+      <c r="B26" s="20" t="s">
+        <v>312</v>
+      </c>
+      <c r="C26" s="20" t="s">
+        <v>314</v>
+      </c>
+      <c r="D26" s="20" t="s">
         <v>317</v>
       </c>
+      <c r="E26" s="20" t="s">
+        <v>319</v>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="14" t="s">
-        <v>320</v>
-      </c>
-      <c r="B27" s="17" t="s">
-        <v>306</v>
-      </c>
-      <c r="C27" s="17" t="s">
+      <c r="A27" s="12" t="s">
         <v>322</v>
       </c>
-      <c r="D27" s="17" t="s">
+      <c r="B27" s="15" t="s">
+        <v>305</v>
+      </c>
+      <c r="C27" s="15" t="s">
+        <v>324</v>
+      </c>
+      <c r="D27" s="15" t="s">
         <v>325</v>
       </c>
-      <c r="E27" s="17" t="s">
-        <v>327</v>
+      <c r="E27" s="15" t="s">
+        <v>326</v>
       </c>
     </row>
     <row r="28"/>
@@ -14752,13 +14714,13 @@
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="46" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B1" s="47"/>
       <c r="C1" s="47"/>
       <c r="D1" s="48"/>
       <c r="E1" s="49" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F1" s="47"/>
       <c r="G1" s="47"/>
@@ -14767,7 +14729,7 @@
       <c r="J1" s="47"/>
       <c r="K1" s="48"/>
       <c r="L1" s="50" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
@@ -14782,48 +14744,48 @@
       <c r="I2" s="52"/>
       <c r="J2" s="52"/>
       <c r="K2" s="53"/>
-      <c r="L2" s="54"/>
+      <c r="L2" s="55"/>
     </row>
     <row r="3" ht="27.75" customHeight="1">
-      <c r="A3" s="55" t="s">
+      <c r="A3" s="56" t="s">
         <v>331</v>
       </c>
-      <c r="B3" s="55" t="s">
+      <c r="B3" s="56" t="s">
         <v>332</v>
       </c>
-      <c r="C3" s="55" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="55" t="s">
+      <c r="C3" s="56" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3" s="56" t="s">
         <v>333</v>
       </c>
-      <c r="E3" s="56" t="s">
+      <c r="E3" s="57" t="s">
         <v>332</v>
       </c>
-      <c r="F3" s="56" t="s">
+      <c r="F3" s="57" t="s">
         <v>334</v>
       </c>
-      <c r="G3" s="56" t="s">
-        <v>39</v>
-      </c>
-      <c r="H3" s="56" t="s">
-        <v>30</v>
-      </c>
-      <c r="I3" s="56" t="s">
+      <c r="G3" s="57" t="s">
+        <v>58</v>
+      </c>
+      <c r="H3" s="57" t="s">
+        <v>51</v>
+      </c>
+      <c r="I3" s="57" t="s">
         <v>335</v>
       </c>
-      <c r="J3" s="56" t="s">
+      <c r="J3" s="57" t="s">
         <v>336</v>
       </c>
-      <c r="K3" s="56" t="s">
-        <v>41</v>
-      </c>
-      <c r="L3" s="57" t="s">
+      <c r="K3" s="57" t="s">
+        <v>61</v>
+      </c>
+      <c r="L3" s="58" t="s">
         <v>337</v>
       </c>
     </row>
     <row r="4" ht="19.5" customHeight="1">
-      <c r="A4" s="58" t="s">
+      <c r="A4" s="59" t="s">
         <v>338</v>
       </c>
       <c r="B4" s="4"/>
@@ -14839,106 +14801,106 @@
       <c r="L4" s="5"/>
     </row>
     <row r="5" ht="78.0" customHeight="1">
-      <c r="A5" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="B5" s="59" t="s">
-        <v>154</v>
-      </c>
-      <c r="C5" s="17" t="s">
-        <v>140</v>
-      </c>
-      <c r="D5" s="38" t="s">
-        <v>339</v>
-      </c>
-      <c r="E5" s="59" t="s">
+      <c r="A5" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="B5" s="60" t="s">
+        <v>149</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="D5" s="37" t="s">
         <v>340</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="E5" s="60" t="s">
         <v>341</v>
       </c>
-      <c r="G5" s="17" t="s">
+      <c r="F5" s="10" t="s">
         <v>342</v>
       </c>
-      <c r="H5" s="17"/>
-      <c r="I5" s="17"/>
-      <c r="J5" s="17"/>
-      <c r="K5" s="17" t="s">
+      <c r="G5" s="15" t="s">
         <v>343</v>
       </c>
-      <c r="L5" s="17" t="s">
+      <c r="H5" s="15"/>
+      <c r="I5" s="15"/>
+      <c r="J5" s="15"/>
+      <c r="K5" s="15" t="s">
         <v>344</v>
       </c>
+      <c r="L5" s="15" t="s">
+        <v>345</v>
+      </c>
     </row>
     <row r="6" ht="78.0" customHeight="1">
-      <c r="A6" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="B6" s="60" t="s">
-        <v>154</v>
+      <c r="A6" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="B6" s="61" t="s">
+        <v>149</v>
       </c>
       <c r="C6" s="62" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="D6" s="62" t="s">
-        <v>347</v>
-      </c>
-      <c r="E6" s="60" t="s">
-        <v>340</v>
-      </c>
-      <c r="F6" s="19" t="s">
-        <v>348</v>
+        <v>349</v>
+      </c>
+      <c r="E6" s="61" t="s">
+        <v>341</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>351</v>
       </c>
       <c r="G6" s="62" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="H6" s="62" t="s">
-        <v>350</v>
-      </c>
-      <c r="I6" s="24"/>
-      <c r="J6" s="24"/>
-      <c r="K6" s="24" t="s">
-        <v>351</v>
-      </c>
-      <c r="L6" s="24" t="s">
-        <v>352</v>
+        <v>353</v>
+      </c>
+      <c r="I6" s="20"/>
+      <c r="J6" s="20"/>
+      <c r="K6" s="20" t="s">
+        <v>357</v>
+      </c>
+      <c r="L6" s="20" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="7" ht="78.0" customHeight="1">
-      <c r="A7" s="14" t="s">
-        <v>123</v>
-      </c>
-      <c r="B7" s="59" t="s">
-        <v>154</v>
-      </c>
-      <c r="C7" s="17" t="s">
-        <v>156</v>
-      </c>
-      <c r="D7" s="17" t="s">
-        <v>353</v>
-      </c>
-      <c r="E7" s="59" t="s">
-        <v>340</v>
-      </c>
-      <c r="F7" s="19" t="s">
-        <v>354</v>
-      </c>
-      <c r="G7" s="17" t="s">
-        <v>355</v>
-      </c>
-      <c r="H7" s="17" t="s">
-        <v>356</v>
-      </c>
-      <c r="I7" s="17"/>
-      <c r="J7" s="17"/>
-      <c r="K7" s="17"/>
-      <c r="L7" s="17" t="s">
-        <v>357</v>
+      <c r="A7" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="B7" s="60" t="s">
+        <v>149</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>361</v>
+      </c>
+      <c r="E7" s="60" t="s">
+        <v>341</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>362</v>
+      </c>
+      <c r="G7" s="15" t="s">
+        <v>363</v>
+      </c>
+      <c r="H7" s="15" t="s">
+        <v>364</v>
+      </c>
+      <c r="I7" s="15"/>
+      <c r="J7" s="15"/>
+      <c r="K7" s="15"/>
+      <c r="L7" s="15" t="s">
+        <v>366</v>
       </c>
     </row>
     <row r="8" ht="19.5" customHeight="1">
-      <c r="A8" s="63" t="s">
-        <v>358</v>
+      <c r="A8" s="64" t="s">
+        <v>368</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
@@ -14953,103 +14915,103 @@
       <c r="L8" s="5"/>
     </row>
     <row r="9" ht="78.0" customHeight="1">
-      <c r="A9" s="14" t="s">
-        <v>152</v>
-      </c>
-      <c r="B9" s="59" t="s">
-        <v>154</v>
-      </c>
-      <c r="C9" s="17" t="s">
-        <v>156</v>
-      </c>
-      <c r="D9" s="17" t="s">
-        <v>359</v>
-      </c>
-      <c r="E9" s="59" t="s">
-        <v>340</v>
-      </c>
-      <c r="F9" s="64" t="s">
-        <v>360</v>
-      </c>
-      <c r="G9" s="17" t="s">
-        <v>361</v>
-      </c>
-      <c r="H9" s="17" t="s">
-        <v>362</v>
-      </c>
-      <c r="I9" s="17"/>
-      <c r="J9" s="17"/>
-      <c r="K9" s="17"/>
-      <c r="L9" s="17" t="s">
-        <v>363</v>
+      <c r="A9" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="B9" s="60" t="s">
+        <v>149</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>378</v>
+      </c>
+      <c r="E9" s="60" t="s">
+        <v>341</v>
+      </c>
+      <c r="F9" s="63" t="s">
+        <v>382</v>
+      </c>
+      <c r="G9" s="15" t="s">
+        <v>385</v>
+      </c>
+      <c r="H9" s="15" t="s">
+        <v>387</v>
+      </c>
+      <c r="I9" s="15"/>
+      <c r="J9" s="15"/>
+      <c r="K9" s="15"/>
+      <c r="L9" s="15" t="s">
+        <v>390</v>
       </c>
     </row>
     <row r="10" ht="78.0" customHeight="1">
-      <c r="A10" s="22" t="s">
-        <v>165</v>
-      </c>
-      <c r="B10" s="60" t="s">
-        <v>154</v>
-      </c>
-      <c r="C10" s="24" t="s">
-        <v>187</v>
+      <c r="A10" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="B10" s="61" t="s">
+        <v>149</v>
+      </c>
+      <c r="C10" s="20" t="s">
+        <v>181</v>
       </c>
       <c r="D10" s="62" t="s">
-        <v>364</v>
-      </c>
-      <c r="E10" s="60" t="s">
-        <v>340</v>
-      </c>
-      <c r="F10" s="19" t="s">
-        <v>365</v>
-      </c>
-      <c r="G10" s="24" t="s">
-        <v>366</v>
-      </c>
-      <c r="H10" s="24" t="s">
-        <v>368</v>
-      </c>
-      <c r="I10" s="24"/>
-      <c r="J10" s="24"/>
-      <c r="K10" s="24" t="s">
-        <v>369</v>
-      </c>
-      <c r="L10" s="24" t="s">
-        <v>370</v>
+        <v>393</v>
+      </c>
+      <c r="E10" s="61" t="s">
+        <v>341</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>396</v>
+      </c>
+      <c r="G10" s="20" t="s">
+        <v>398</v>
+      </c>
+      <c r="H10" s="20" t="s">
+        <v>400</v>
+      </c>
+      <c r="I10" s="20"/>
+      <c r="J10" s="20"/>
+      <c r="K10" s="20" t="s">
+        <v>402</v>
+      </c>
+      <c r="L10" s="20" t="s">
+        <v>403</v>
       </c>
     </row>
     <row r="11" ht="78.0" customHeight="1">
-      <c r="A11" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="B11" s="59" t="s">
-        <v>154</v>
-      </c>
-      <c r="C11" s="17" t="s">
-        <v>371</v>
-      </c>
-      <c r="D11" s="17" t="s">
-        <v>372</v>
-      </c>
-      <c r="E11" s="59" t="s">
-        <v>340</v>
-      </c>
-      <c r="F11" s="19" t="s">
-        <v>373</v>
-      </c>
-      <c r="G11" s="17" t="s">
-        <v>374</v>
-      </c>
-      <c r="H11" s="17" t="s">
-        <v>375</v>
-      </c>
-      <c r="I11" s="17" t="s">
-        <v>376</v>
-      </c>
-      <c r="J11" s="17"/>
-      <c r="K11" s="17"/>
-      <c r="L11" s="17" t="s">
-        <v>378</v>
+      <c r="A11" s="12" t="s">
+        <v>178</v>
+      </c>
+      <c r="B11" s="60" t="s">
+        <v>149</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>404</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>405</v>
+      </c>
+      <c r="E11" s="60" t="s">
+        <v>341</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>406</v>
+      </c>
+      <c r="G11" s="15" t="s">
+        <v>407</v>
+      </c>
+      <c r="H11" s="15" t="s">
+        <v>408</v>
+      </c>
+      <c r="I11" s="15" t="s">
+        <v>409</v>
+      </c>
+      <c r="J11" s="15"/>
+      <c r="K11" s="15"/>
+      <c r="L11" s="15" t="s">
+        <v>410</v>
       </c>
     </row>
     <row r="21"/>
@@ -16071,14 +16033,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="61" t="s">
-        <v>345</v>
+      <c r="A1" s="54" t="s">
+        <v>330</v>
       </c>
       <c r="B1" s="47"/>
       <c r="C1" s="47"/>
       <c r="D1" s="48"/>
       <c r="E1" s="49" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F1" s="47"/>
       <c r="G1" s="47"/>
@@ -16087,7 +16049,7 @@
       <c r="J1" s="47"/>
       <c r="K1" s="48"/>
       <c r="L1" s="50" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
@@ -16102,49 +16064,49 @@
       <c r="I2" s="52"/>
       <c r="J2" s="52"/>
       <c r="K2" s="53"/>
-      <c r="L2" s="54"/>
+      <c r="L2" s="55"/>
     </row>
     <row r="3" ht="27.75" customHeight="1">
-      <c r="A3" s="55" t="s">
+      <c r="A3" s="56" t="s">
         <v>331</v>
       </c>
-      <c r="B3" s="55" t="s">
+      <c r="B3" s="56" t="s">
         <v>332</v>
       </c>
-      <c r="C3" s="55" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="55" t="s">
+      <c r="C3" s="56" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3" s="56" t="s">
         <v>333</v>
       </c>
-      <c r="E3" s="56" t="s">
+      <c r="E3" s="57" t="s">
         <v>332</v>
       </c>
-      <c r="F3" s="56" t="s">
+      <c r="F3" s="57" t="s">
         <v>334</v>
       </c>
-      <c r="G3" s="56" t="s">
-        <v>39</v>
-      </c>
-      <c r="H3" s="56" t="s">
-        <v>30</v>
-      </c>
-      <c r="I3" s="56" t="s">
+      <c r="G3" s="57" t="s">
+        <v>58</v>
+      </c>
+      <c r="H3" s="57" t="s">
+        <v>51</v>
+      </c>
+      <c r="I3" s="57" t="s">
         <v>335</v>
       </c>
-      <c r="J3" s="56" t="s">
+      <c r="J3" s="57" t="s">
         <v>336</v>
       </c>
-      <c r="K3" s="56" t="s">
-        <v>41</v>
-      </c>
-      <c r="L3" s="57" t="s">
+      <c r="K3" s="57" t="s">
+        <v>61</v>
+      </c>
+      <c r="L3" s="58" t="s">
         <v>337</v>
       </c>
     </row>
     <row r="4" ht="19.5" customHeight="1">
-      <c r="A4" s="58" t="s">
-        <v>367</v>
+      <c r="A4" s="59" t="s">
+        <v>339</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -16159,147 +16121,147 @@
       <c r="L4" s="5"/>
     </row>
     <row r="5" ht="78.0" customHeight="1">
-      <c r="A5" s="14" t="s">
+      <c r="A5" s="12" t="s">
+        <v>346</v>
+      </c>
+      <c r="B5" s="60" t="s">
+        <v>149</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>347</v>
+      </c>
+      <c r="E5" s="60" t="s">
+        <v>341</v>
+      </c>
+      <c r="F5" s="63" t="s">
+        <v>350</v>
+      </c>
+      <c r="G5" s="15" t="s">
+        <v>354</v>
+      </c>
+      <c r="H5" s="15" t="s">
+        <v>355</v>
+      </c>
+      <c r="I5" s="15" t="s">
+        <v>356</v>
+      </c>
+      <c r="J5" s="15"/>
+      <c r="K5" s="15"/>
+      <c r="L5" s="15" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="6" ht="78.0" customHeight="1">
+      <c r="A6" s="19" t="s">
+        <v>360</v>
+      </c>
+      <c r="B6" s="61" t="s">
+        <v>149</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>365</v>
+      </c>
+      <c r="D6" s="62" t="s">
+        <v>367</v>
+      </c>
+      <c r="E6" s="61" t="s">
+        <v>341</v>
+      </c>
+      <c r="F6" s="63" t="s">
+        <v>369</v>
+      </c>
+      <c r="G6" s="20" t="s">
+        <v>370</v>
+      </c>
+      <c r="H6" s="20" t="s">
+        <v>371</v>
+      </c>
+      <c r="I6" s="20" t="s">
+        <v>372</v>
+      </c>
+      <c r="J6" s="20" t="s">
+        <v>373</v>
+      </c>
+      <c r="K6" s="20"/>
+      <c r="L6" s="20" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="7" ht="78.0" customHeight="1">
+      <c r="A7" s="12" t="s">
+        <v>375</v>
+      </c>
+      <c r="B7" s="60" t="s">
+        <v>149</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>376</v>
+      </c>
+      <c r="D7" s="37" t="s">
         <v>377</v>
       </c>
-      <c r="B5" s="59" t="s">
-        <v>154</v>
-      </c>
-      <c r="C5" s="17" t="s">
-        <v>156</v>
-      </c>
-      <c r="D5" s="17" t="s">
+      <c r="E7" s="60" t="s">
+        <v>341</v>
+      </c>
+      <c r="F7" s="10" t="s">
         <v>379</v>
       </c>
-      <c r="E5" s="59" t="s">
-        <v>340</v>
-      </c>
-      <c r="F5" s="64" t="s">
+      <c r="G7" s="15" t="s">
         <v>380</v>
       </c>
-      <c r="G5" s="17" t="s">
+      <c r="H7" s="15" t="s">
         <v>381</v>
       </c>
-      <c r="H5" s="17" t="s">
-        <v>382</v>
-      </c>
-      <c r="I5" s="17" t="s">
+      <c r="I7" s="15" t="s">
         <v>383</v>
       </c>
-      <c r="J5" s="17"/>
-      <c r="K5" s="17"/>
-      <c r="L5" s="17" t="s">
+      <c r="J7" s="15" t="s">
         <v>384</v>
       </c>
-    </row>
-    <row r="6" ht="78.0" customHeight="1">
-      <c r="A6" s="22" t="s">
-        <v>385</v>
-      </c>
-      <c r="B6" s="60" t="s">
-        <v>154</v>
-      </c>
-      <c r="C6" s="24" t="s">
+      <c r="K7" s="15" t="s">
         <v>386</v>
       </c>
-      <c r="D6" s="62" t="s">
-        <v>387</v>
-      </c>
-      <c r="E6" s="60" t="s">
-        <v>340</v>
-      </c>
-      <c r="F6" s="64" t="s">
+      <c r="L7" s="15" t="s">
         <v>388</v>
       </c>
-      <c r="G6" s="24" t="s">
+    </row>
+    <row r="8" ht="78.0" customHeight="1">
+      <c r="A8" s="19" t="s">
         <v>389</v>
       </c>
-      <c r="H6" s="24" t="s">
-        <v>390</v>
-      </c>
-      <c r="I6" s="24" t="s">
+      <c r="B8" s="61" t="s">
+        <v>149</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>365</v>
+      </c>
+      <c r="D8" s="62" t="s">
         <v>391</v>
       </c>
-      <c r="J6" s="24" t="s">
+      <c r="E8" s="61" t="s">
+        <v>341</v>
+      </c>
+      <c r="F8" s="10" t="s">
         <v>392</v>
       </c>
-      <c r="K6" s="24"/>
-      <c r="L6" s="24" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="7" ht="78.0" customHeight="1">
-      <c r="A7" s="14" t="s">
+      <c r="G8" s="20" t="s">
         <v>394</v>
       </c>
-      <c r="B7" s="59" t="s">
-        <v>154</v>
-      </c>
-      <c r="C7" s="17" t="s">
+      <c r="H8" s="20" t="s">
         <v>395</v>
       </c>
-      <c r="D7" s="38" t="s">
-        <v>396</v>
-      </c>
-      <c r="E7" s="59" t="s">
-        <v>340</v>
-      </c>
-      <c r="F7" s="19" t="s">
+      <c r="I8" s="20" t="s">
         <v>397</v>
       </c>
-      <c r="G7" s="17" t="s">
-        <v>398</v>
-      </c>
-      <c r="H7" s="17" t="s">
+      <c r="J8" s="20" t="s">
         <v>399</v>
       </c>
-      <c r="I7" s="17" t="s">
-        <v>400</v>
-      </c>
-      <c r="J7" s="17" t="s">
+      <c r="K8" s="20"/>
+      <c r="L8" s="20" t="s">
         <v>401</v>
-      </c>
-      <c r="K7" s="17" t="s">
-        <v>402</v>
-      </c>
-      <c r="L7" s="17" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="8" ht="78.0" customHeight="1">
-      <c r="A8" s="22" t="s">
-        <v>404</v>
-      </c>
-      <c r="B8" s="60" t="s">
-        <v>154</v>
-      </c>
-      <c r="C8" s="24" t="s">
-        <v>386</v>
-      </c>
-      <c r="D8" s="62" t="s">
-        <v>405</v>
-      </c>
-      <c r="E8" s="60" t="s">
-        <v>340</v>
-      </c>
-      <c r="F8" s="19" t="s">
-        <v>406</v>
-      </c>
-      <c r="G8" s="24" t="s">
-        <v>407</v>
-      </c>
-      <c r="H8" s="24" t="s">
-        <v>408</v>
-      </c>
-      <c r="I8" s="24" t="s">
-        <v>409</v>
-      </c>
-      <c r="J8" s="24" t="s">
-        <v>410</v>
-      </c>
-      <c r="K8" s="24"/>
-      <c r="L8" s="24" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="21"/>
@@ -17320,14 +17282,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="61" t="s">
-        <v>345</v>
+      <c r="A1" s="54" t="s">
+        <v>330</v>
       </c>
       <c r="B1" s="47"/>
       <c r="C1" s="47"/>
       <c r="D1" s="48"/>
       <c r="E1" s="49" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F1" s="47"/>
       <c r="G1" s="47"/>
@@ -17336,7 +17298,7 @@
       <c r="J1" s="47"/>
       <c r="K1" s="48"/>
       <c r="L1" s="50" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
@@ -17351,49 +17313,49 @@
       <c r="I2" s="52"/>
       <c r="J2" s="52"/>
       <c r="K2" s="53"/>
-      <c r="L2" s="54"/>
+      <c r="L2" s="55"/>
     </row>
     <row r="3" ht="27.75" customHeight="1">
-      <c r="A3" s="55" t="s">
+      <c r="A3" s="56" t="s">
         <v>331</v>
       </c>
-      <c r="B3" s="55" t="s">
+      <c r="B3" s="56" t="s">
         <v>332</v>
       </c>
-      <c r="C3" s="55" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="55" t="s">
+      <c r="C3" s="56" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3" s="56" t="s">
         <v>333</v>
       </c>
-      <c r="E3" s="56" t="s">
+      <c r="E3" s="57" t="s">
         <v>332</v>
       </c>
-      <c r="F3" s="56" t="s">
+      <c r="F3" s="57" t="s">
         <v>334</v>
       </c>
-      <c r="G3" s="56" t="s">
-        <v>39</v>
-      </c>
-      <c r="H3" s="56" t="s">
-        <v>30</v>
-      </c>
-      <c r="I3" s="56" t="s">
+      <c r="G3" s="57" t="s">
+        <v>58</v>
+      </c>
+      <c r="H3" s="57" t="s">
+        <v>51</v>
+      </c>
+      <c r="I3" s="57" t="s">
         <v>335</v>
       </c>
-      <c r="J3" s="56" t="s">
+      <c r="J3" s="57" t="s">
         <v>336</v>
       </c>
-      <c r="K3" s="56" t="s">
-        <v>41</v>
-      </c>
-      <c r="L3" s="57" t="s">
+      <c r="K3" s="57" t="s">
+        <v>61</v>
+      </c>
+      <c r="L3" s="58" t="s">
         <v>337</v>
       </c>
     </row>
     <row r="4" ht="19.5" customHeight="1">
-      <c r="A4" s="58" t="s">
-        <v>412</v>
+      <c r="A4" s="59" t="s">
+        <v>411</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -17408,189 +17370,189 @@
       <c r="L4" s="5"/>
     </row>
     <row r="5" ht="78.0" customHeight="1">
-      <c r="A5" s="14" t="s">
+      <c r="A5" s="12" t="s">
+        <v>412</v>
+      </c>
+      <c r="B5" s="60" t="s">
+        <v>149</v>
+      </c>
+      <c r="C5" s="15" t="s">
         <v>413</v>
       </c>
-      <c r="B5" s="59" t="s">
-        <v>154</v>
-      </c>
-      <c r="C5" s="17" t="s">
+      <c r="D5" s="15" t="s">
         <v>414</v>
       </c>
-      <c r="D5" s="17" t="s">
+      <c r="E5" s="60" t="s">
+        <v>341</v>
+      </c>
+      <c r="F5" s="10" t="s">
         <v>415</v>
       </c>
-      <c r="E5" s="59" t="s">
-        <v>340</v>
-      </c>
-      <c r="F5" s="19" t="s">
+      <c r="G5" s="15" t="s">
         <v>416</v>
       </c>
-      <c r="G5" s="17" t="s">
+      <c r="H5" s="15" t="s">
         <v>417</v>
       </c>
-      <c r="H5" s="17" t="s">
+      <c r="I5" s="15" t="s">
         <v>418</v>
       </c>
-      <c r="I5" s="17" t="s">
+      <c r="J5" s="15"/>
+      <c r="K5" s="15" t="s">
         <v>419</v>
       </c>
-      <c r="J5" s="17"/>
-      <c r="K5" s="17" t="s">
+      <c r="L5" s="15" t="s">
         <v>420</v>
       </c>
-      <c r="L5" s="17" t="s">
+    </row>
+    <row r="6" ht="78.0" customHeight="1">
+      <c r="A6" s="19" t="s">
         <v>421</v>
       </c>
-    </row>
-    <row r="6" ht="78.0" customHeight="1">
-      <c r="A6" s="22" t="s">
+      <c r="B6" s="61" t="s">
+        <v>149</v>
+      </c>
+      <c r="C6" s="20" t="s">
         <v>422</v>
       </c>
-      <c r="B6" s="60" t="s">
-        <v>154</v>
-      </c>
-      <c r="C6" s="24" t="s">
+      <c r="D6" s="20" t="s">
         <v>423</v>
       </c>
-      <c r="D6" s="24" t="s">
+      <c r="E6" s="61" t="s">
+        <v>341</v>
+      </c>
+      <c r="F6" s="10" t="s">
         <v>424</v>
       </c>
-      <c r="E6" s="60" t="s">
-        <v>340</v>
-      </c>
-      <c r="F6" s="19" t="s">
+      <c r="G6" s="20" t="s">
         <v>425</v>
       </c>
-      <c r="G6" s="24" t="s">
+      <c r="H6" s="20" t="s">
         <v>426</v>
       </c>
-      <c r="H6" s="24" t="s">
+      <c r="I6" s="20"/>
+      <c r="J6" s="20"/>
+      <c r="K6" s="20"/>
+      <c r="L6" s="20" t="s">
         <v>427</v>
       </c>
-      <c r="I6" s="24"/>
-      <c r="J6" s="24"/>
-      <c r="K6" s="24"/>
-      <c r="L6" s="24" t="s">
+      <c r="M6" s="34" t="s">
         <v>428</v>
       </c>
-      <c r="M6" s="34" t="s">
+    </row>
+    <row r="7" ht="78.0" customHeight="1">
+      <c r="A7" s="12" t="s">
         <v>429</v>
       </c>
-    </row>
-    <row r="7" ht="78.0" customHeight="1">
-      <c r="A7" s="14" t="s">
+      <c r="B7" s="60" t="s">
+        <v>149</v>
+      </c>
+      <c r="C7" s="15" t="s">
         <v>430</v>
       </c>
-      <c r="B7" s="59" t="s">
-        <v>154</v>
-      </c>
-      <c r="C7" s="17" t="s">
+      <c r="D7" s="15" t="s">
         <v>431</v>
       </c>
-      <c r="D7" s="17" t="s">
+      <c r="E7" s="60" t="s">
+        <v>341</v>
+      </c>
+      <c r="F7" s="10" t="s">
         <v>432</v>
       </c>
-      <c r="E7" s="59" t="s">
-        <v>340</v>
-      </c>
-      <c r="F7" s="19" t="s">
+      <c r="G7" s="15" t="s">
         <v>433</v>
       </c>
-      <c r="G7" s="17" t="s">
+      <c r="H7" s="15" t="s">
         <v>434</v>
       </c>
-      <c r="H7" s="17" t="s">
+      <c r="I7" s="15"/>
+      <c r="J7" s="15" t="s">
         <v>435</v>
       </c>
-      <c r="I7" s="17"/>
-      <c r="J7" s="17" t="s">
+      <c r="K7" s="15"/>
+      <c r="L7" s="15" t="s">
         <v>436</v>
       </c>
-      <c r="K7" s="17"/>
-      <c r="L7" s="17" t="s">
+    </row>
+    <row r="8" ht="78.0" customHeight="1">
+      <c r="A8" s="19" t="s">
         <v>437</v>
       </c>
-    </row>
-    <row r="8" ht="78.0" customHeight="1">
-      <c r="A8" s="22" t="s">
+      <c r="B8" s="61" t="s">
+        <v>149</v>
+      </c>
+      <c r="C8" s="20" t="s">
         <v>438</v>
       </c>
-      <c r="B8" s="60" t="s">
-        <v>154</v>
-      </c>
-      <c r="C8" s="24" t="s">
+      <c r="D8" s="20" t="s">
         <v>439</v>
       </c>
-      <c r="D8" s="24" t="s">
+      <c r="E8" s="61" t="s">
+        <v>341</v>
+      </c>
+      <c r="F8" s="10" t="s">
         <v>440</v>
       </c>
-      <c r="E8" s="60" t="s">
-        <v>340</v>
-      </c>
-      <c r="F8" s="19" t="s">
+      <c r="G8" s="20" t="s">
         <v>441</v>
       </c>
-      <c r="G8" s="24" t="s">
+      <c r="H8" s="20" t="s">
         <v>442</v>
       </c>
-      <c r="H8" s="24" t="s">
+      <c r="I8" s="20" t="s">
         <v>443</v>
       </c>
-      <c r="I8" s="24" t="s">
+      <c r="J8" s="20" t="s">
         <v>444</v>
       </c>
-      <c r="J8" s="24" t="s">
+      <c r="K8" s="20" t="s">
         <v>445</v>
       </c>
-      <c r="K8" s="24" t="s">
+      <c r="L8" s="20" t="s">
         <v>446</v>
       </c>
-      <c r="L8" s="24" t="s">
+    </row>
+    <row r="9" ht="78.0" customHeight="1">
+      <c r="A9" s="12" t="s">
         <v>447</v>
       </c>
-    </row>
-    <row r="9" ht="78.0" customHeight="1">
-      <c r="A9" s="14" t="s">
+      <c r="B9" s="60" t="s">
+        <v>149</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>430</v>
+      </c>
+      <c r="D9" s="15" t="s">
         <v>448</v>
       </c>
-      <c r="B9" s="59" t="s">
-        <v>154</v>
-      </c>
-      <c r="C9" s="17" t="s">
-        <v>431</v>
-      </c>
-      <c r="D9" s="17" t="s">
+      <c r="E9" s="60" t="s">
+        <v>341</v>
+      </c>
+      <c r="F9" s="10" t="s">
         <v>449</v>
       </c>
-      <c r="E9" s="59" t="s">
-        <v>340</v>
-      </c>
-      <c r="F9" s="19" t="s">
+      <c r="G9" s="15" t="s">
         <v>450</v>
       </c>
-      <c r="G9" s="17" t="s">
+      <c r="H9" s="15" t="s">
         <v>451</v>
       </c>
-      <c r="H9" s="17" t="s">
+      <c r="I9" s="15" t="s">
         <v>452</v>
       </c>
-      <c r="I9" s="17" t="s">
+      <c r="J9" s="15" t="s">
         <v>453</v>
       </c>
-      <c r="J9" s="17" t="s">
+      <c r="K9" s="15" t="s">
         <v>454</v>
       </c>
-      <c r="K9" s="17" t="s">
+      <c r="L9" s="15" t="s">
         <v>455</v>
-      </c>
-      <c r="L9" s="17" t="s">
-        <v>456</v>
       </c>
     </row>
     <row r="10">
       <c r="C10" s="65" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="21"/>
@@ -18611,14 +18573,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="61" t="s">
-        <v>345</v>
+      <c r="A1" s="54" t="s">
+        <v>330</v>
       </c>
       <c r="B1" s="47"/>
       <c r="C1" s="47"/>
       <c r="D1" s="48"/>
       <c r="E1" s="49" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F1" s="47"/>
       <c r="G1" s="47"/>
@@ -18627,7 +18589,7 @@
       <c r="J1" s="47"/>
       <c r="K1" s="48"/>
       <c r="L1" s="50" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
@@ -18642,49 +18604,49 @@
       <c r="I2" s="52"/>
       <c r="J2" s="52"/>
       <c r="K2" s="53"/>
-      <c r="L2" s="54"/>
+      <c r="L2" s="55"/>
     </row>
     <row r="3" ht="27.75" customHeight="1">
-      <c r="A3" s="55" t="s">
+      <c r="A3" s="56" t="s">
         <v>331</v>
       </c>
-      <c r="B3" s="55" t="s">
+      <c r="B3" s="56" t="s">
         <v>332</v>
       </c>
-      <c r="C3" s="55" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="55" t="s">
+      <c r="C3" s="56" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3" s="56" t="s">
         <v>333</v>
       </c>
-      <c r="E3" s="56" t="s">
+      <c r="E3" s="57" t="s">
         <v>332</v>
       </c>
-      <c r="F3" s="56" t="s">
+      <c r="F3" s="57" t="s">
         <v>334</v>
       </c>
-      <c r="G3" s="56" t="s">
-        <v>39</v>
-      </c>
-      <c r="H3" s="56" t="s">
-        <v>30</v>
-      </c>
-      <c r="I3" s="56" t="s">
+      <c r="G3" s="57" t="s">
+        <v>58</v>
+      </c>
+      <c r="H3" s="57" t="s">
+        <v>51</v>
+      </c>
+      <c r="I3" s="57" t="s">
         <v>335</v>
       </c>
-      <c r="J3" s="56" t="s">
+      <c r="J3" s="57" t="s">
         <v>336</v>
       </c>
-      <c r="K3" s="56" t="s">
-        <v>41</v>
-      </c>
-      <c r="L3" s="57" t="s">
+      <c r="K3" s="57" t="s">
+        <v>61</v>
+      </c>
+      <c r="L3" s="58" t="s">
         <v>337</v>
       </c>
     </row>
     <row r="4" ht="19.5" customHeight="1">
-      <c r="A4" s="58" t="s">
-        <v>458</v>
+      <c r="A4" s="59" t="s">
+        <v>457</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -18699,219 +18661,219 @@
       <c r="L4" s="5"/>
     </row>
     <row r="5" ht="78.0" customHeight="1">
-      <c r="A5" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="B5" s="59" t="s">
-        <v>154</v>
-      </c>
-      <c r="C5" s="17" t="s">
+      <c r="A5" s="12" t="s">
+        <v>298</v>
+      </c>
+      <c r="B5" s="60" t="s">
+        <v>149</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>458</v>
+      </c>
+      <c r="D5" s="15" t="s">
         <v>459</v>
       </c>
-      <c r="D5" s="17" t="s">
+      <c r="E5" s="60" t="s">
+        <v>341</v>
+      </c>
+      <c r="F5" s="10" t="s">
         <v>460</v>
       </c>
-      <c r="E5" s="59" t="s">
-        <v>340</v>
-      </c>
-      <c r="F5" s="19" t="s">
+      <c r="G5" s="15" t="s">
         <v>461</v>
       </c>
-      <c r="G5" s="17" t="s">
+      <c r="H5" s="15" t="s">
         <v>462</v>
       </c>
-      <c r="H5" s="17" t="s">
+      <c r="I5" s="15"/>
+      <c r="J5" s="15" t="s">
         <v>463</v>
       </c>
-      <c r="I5" s="17"/>
-      <c r="J5" s="17" t="s">
+      <c r="K5" s="15"/>
+      <c r="L5" s="15" t="s">
         <v>464</v>
       </c>
-      <c r="K5" s="17"/>
-      <c r="L5" s="17" t="s">
+    </row>
+    <row r="6" ht="78.0" customHeight="1">
+      <c r="A6" s="19" t="s">
         <v>465</v>
       </c>
-    </row>
-    <row r="6" ht="78.0" customHeight="1">
-      <c r="A6" s="22" t="s">
+      <c r="B6" s="61" t="s">
+        <v>149</v>
+      </c>
+      <c r="C6" s="20" t="s">
         <v>466</v>
       </c>
-      <c r="B6" s="60" t="s">
-        <v>154</v>
-      </c>
-      <c r="C6" s="24" t="s">
+      <c r="D6" s="20" t="s">
         <v>467</v>
       </c>
-      <c r="D6" s="24" t="s">
+      <c r="E6" s="61" t="s">
+        <v>341</v>
+      </c>
+      <c r="F6" s="10" t="s">
         <v>468</v>
       </c>
-      <c r="E6" s="60" t="s">
-        <v>340</v>
-      </c>
-      <c r="F6" s="19" t="s">
+      <c r="G6" s="20" t="s">
         <v>469</v>
       </c>
-      <c r="G6" s="24" t="s">
+      <c r="H6" s="20" t="s">
         <v>470</v>
       </c>
-      <c r="H6" s="24" t="s">
+      <c r="I6" s="20"/>
+      <c r="J6" s="20" t="s">
         <v>471</v>
       </c>
-      <c r="I6" s="24"/>
-      <c r="J6" s="24" t="s">
+      <c r="K6" s="20" t="s">
         <v>472</v>
       </c>
-      <c r="K6" s="24" t="s">
+      <c r="L6" s="20" t="s">
         <v>473</v>
       </c>
-      <c r="L6" s="24" t="s">
+    </row>
+    <row r="7" ht="78.0" customHeight="1">
+      <c r="A7" s="12" t="s">
         <v>474</v>
       </c>
-    </row>
-    <row r="7" ht="78.0" customHeight="1">
-      <c r="A7" s="14" t="s">
+      <c r="B7" s="60" t="s">
+        <v>149</v>
+      </c>
+      <c r="C7" s="15" t="s">
         <v>475</v>
       </c>
-      <c r="B7" s="59" t="s">
-        <v>154</v>
-      </c>
-      <c r="C7" s="17" t="s">
+      <c r="D7" s="15" t="s">
         <v>476</v>
       </c>
-      <c r="D7" s="17" t="s">
+      <c r="E7" s="60" t="s">
+        <v>341</v>
+      </c>
+      <c r="F7" s="63" t="s">
         <v>477</v>
       </c>
-      <c r="E7" s="59" t="s">
-        <v>340</v>
-      </c>
-      <c r="F7" s="64" t="s">
+      <c r="G7" s="15" t="s">
         <v>478</v>
       </c>
-      <c r="G7" s="17" t="s">
+      <c r="H7" s="15" t="s">
         <v>479</v>
       </c>
-      <c r="H7" s="17" t="s">
+      <c r="I7" s="15" t="s">
         <v>480</v>
       </c>
-      <c r="I7" s="17" t="s">
+      <c r="J7" s="15"/>
+      <c r="K7" s="15"/>
+      <c r="L7" s="15" t="s">
         <v>481</v>
       </c>
-      <c r="J7" s="17"/>
-      <c r="K7" s="17"/>
-      <c r="L7" s="17" t="s">
+    </row>
+    <row r="8" ht="78.0" customHeight="1">
+      <c r="A8" s="19" t="s">
         <v>482</v>
       </c>
-    </row>
-    <row r="8" ht="78.0" customHeight="1">
-      <c r="A8" s="22" t="s">
+      <c r="B8" s="61" t="s">
+        <v>149</v>
+      </c>
+      <c r="C8" s="20" t="s">
         <v>483</v>
       </c>
-      <c r="B8" s="60" t="s">
-        <v>154</v>
-      </c>
-      <c r="C8" s="24" t="s">
+      <c r="D8" s="20" t="s">
         <v>484</v>
       </c>
-      <c r="D8" s="24" t="s">
+      <c r="E8" s="61" t="s">
+        <v>341</v>
+      </c>
+      <c r="F8" s="63" t="s">
         <v>485</v>
       </c>
-      <c r="E8" s="60" t="s">
-        <v>340</v>
-      </c>
-      <c r="F8" s="64" t="s">
+      <c r="G8" s="20" t="s">
         <v>486</v>
       </c>
-      <c r="G8" s="24" t="s">
+      <c r="H8" s="20" t="s">
         <v>487</v>
       </c>
-      <c r="H8" s="24" t="s">
+      <c r="I8" s="20" t="s">
         <v>488</v>
       </c>
-      <c r="I8" s="24" t="s">
+      <c r="J8" s="20" t="s">
         <v>489</v>
       </c>
-      <c r="J8" s="24" t="s">
+      <c r="K8" s="20"/>
+      <c r="L8" s="20" t="s">
         <v>490</v>
       </c>
-      <c r="K8" s="24"/>
-      <c r="L8" s="24" t="s">
+    </row>
+    <row r="9" ht="78.0" customHeight="1">
+      <c r="A9" s="12" t="s">
         <v>491</v>
       </c>
-    </row>
-    <row r="9" ht="78.0" customHeight="1">
-      <c r="A9" s="14" t="s">
+      <c r="B9" s="60" t="s">
+        <v>149</v>
+      </c>
+      <c r="C9" s="15" t="s">
         <v>492</v>
       </c>
-      <c r="B9" s="59" t="s">
-        <v>154</v>
-      </c>
-      <c r="C9" s="17" t="s">
+      <c r="D9" s="15" t="s">
         <v>493</v>
       </c>
-      <c r="D9" s="17" t="s">
+      <c r="E9" s="60" t="s">
+        <v>341</v>
+      </c>
+      <c r="F9" s="10" t="s">
         <v>494</v>
       </c>
-      <c r="E9" s="59" t="s">
-        <v>340</v>
-      </c>
-      <c r="F9" s="19" t="s">
+      <c r="G9" s="15" t="s">
         <v>495</v>
       </c>
-      <c r="G9" s="17" t="s">
+      <c r="H9" s="15" t="s">
         <v>496</v>
       </c>
-      <c r="H9" s="17" t="s">
+      <c r="I9" s="15" t="s">
         <v>497</v>
       </c>
-      <c r="I9" s="17" t="s">
+      <c r="J9" s="15" t="s">
         <v>498</v>
       </c>
-      <c r="J9" s="17" t="s">
+      <c r="K9" s="15" t="s">
         <v>499</v>
       </c>
-      <c r="K9" s="17" t="s">
+      <c r="L9" s="15" t="s">
         <v>500</v>
       </c>
-      <c r="L9" s="17" t="s">
+    </row>
+    <row r="10" ht="78.0" customHeight="1">
+      <c r="A10" s="19" t="s">
         <v>501</v>
       </c>
-    </row>
-    <row r="10" ht="78.0" customHeight="1">
-      <c r="A10" s="22" t="s">
+      <c r="B10" s="61" t="s">
+        <v>149</v>
+      </c>
+      <c r="C10" s="20" t="s">
+        <v>483</v>
+      </c>
+      <c r="D10" s="20" t="s">
         <v>502</v>
       </c>
-      <c r="B10" s="60" t="s">
-        <v>154</v>
-      </c>
-      <c r="C10" s="24" t="s">
-        <v>484</v>
-      </c>
-      <c r="D10" s="24" t="s">
+      <c r="E10" s="61" t="s">
+        <v>341</v>
+      </c>
+      <c r="F10" s="10" t="s">
         <v>503</v>
       </c>
-      <c r="E10" s="60" t="s">
-        <v>340</v>
-      </c>
-      <c r="F10" s="19" t="s">
+      <c r="G10" s="20" t="s">
         <v>504</v>
       </c>
-      <c r="G10" s="24" t="s">
+      <c r="H10" s="20" t="s">
         <v>505</v>
       </c>
-      <c r="H10" s="24" t="s">
+      <c r="I10" s="20" t="s">
         <v>506</v>
       </c>
-      <c r="I10" s="24" t="s">
+      <c r="J10" s="20" t="s">
         <v>507</v>
       </c>
-      <c r="J10" s="24" t="s">
+      <c r="K10" s="20" t="s">
         <v>508</v>
       </c>
-      <c r="K10" s="24" t="s">
+      <c r="L10" s="20" t="s">
         <v>509</v>
-      </c>
-      <c r="L10" s="24" t="s">
-        <v>510</v>
       </c>
     </row>
     <row r="21"/>
